--- a/data/xlsx/representative_2022.xlsx
+++ b/data/xlsx/representative_2022.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2797">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -3051,7 +3051,7 @@
     <t>Bukit Kayu Hitam</t>
   </si>
   <si>
-    <t>Halimaton Shaadiah Saad|link=Halimaton Shaadiah Saad}}</t>
+    <t>Halimaton Shaadiah Saad</t>
   </si>
   <si>
     <t>Bukit Kayu Hitam;FELDA Bukit Tangga;Temin;FELDA Laka Selatan;FELDA Batu Lapan;Pekan Baru Changlun;Pekan Lama Changlun;Sintok;Kampung Darat;Kubang Pasu;Guar Napai;Husba;Kampung Napoh;Binjal;Kampung Bemban;Pulau Pisang;Pekan Tunjang;Pulau Timbol;Padang Limau;Pulau Nyior;Kampung Pulau Ketam;Gelong Rambai</t>
@@ -3096,7 +3096,7 @@
     <t>Bukit Pinang</t>
   </si>
   <si>
-    <t>Wan Romani Wan Salim|link=Wan Romani Wan Salim}}</t>
+    <t>Wan Romani Wan Salim</t>
   </si>
   <si>
     <t>Paya Lengkuas;Bukit Pinang;Titi Baru;Kubang Lintah;Hutan Kampung;Taman Bayu;Kampung Bohor;Lepai;Kampung Sungai Mati;Limbong;Kampung Alor Setol;Pondok Langgar;Kampung Langgar B;Telok Jamat;Alor Senibong;Tualang</t>
@@ -3132,7 +3132,7 @@
     <t>Alor Mengkudu</t>
   </si>
   <si>
-    <t>Muhamad Radhi Mat Din|link=Muhamad Radhi Mat Din}}</t>
+    <t>Muhamad Radhi Mat Din</t>
   </si>
   <si>
     <t>Kampung Gelam;Alor Melintang;Titi Haji Idris;Tok Sibil;Alor Binjal;Tok Keling;Lahar Budi;Alor Mengkudu;Taman Saga;Taman Sultan Abdul Halim;Jalan Langgar;Kampung Tanjong Bendahara;Keriang Pulau;Selarong;Tandop</t>
@@ -3177,7 +3177,7 @@
     <t>Tokai</t>
   </si>
   <si>
-    <t>Mohd Hayati Othman|link=Mohd Hayati Othman}}</t>
+    <t>Mohd Hayati Othman</t>
   </si>
   <si>
     <t>Sri Pudak;Kepala Bukit;Kampung Penyarom;Tanah Merah;Kampung Rambai;Kubang Jelai;Pekan Tokai;Kampung Pulai;Alor Besar;Kobah;Tempoyak;Sebrang Pendang;Pekan Pendang;Bukit Raya;Banggol Besi;Guar Kepayang;Cherok Kudong;Gajah Mati;Manggol Petai;Paya Kelubi;Batu Manunggul</t>
@@ -3225,7 +3225,7 @@
     <t>Gurun</t>
   </si>
   <si>
-    <t>Baddrol Bakhtiar|link=Baddrol Bakhtiar}}</t>
+    <t>Baddrol Bakhtiar</t>
   </si>
   <si>
     <t>Pekan Jeniang;Kampung Jeniang;Batu Sepuloh;Batu 9;Padang Lembu;Sungai Rotan;Gurun;Pulau Chengai;Bongkok Gurun;Pekan Gurun;Pekan Baru Gurun;Kampung Gurun;Taman Seri Jerai;Ladang Jerai;Sungai Puntar;Sungai Tok Pawang;Kampung Mesjid;Pekan Bahru Bedong</t>
@@ -3249,7 +3249,7 @@
     <t>Jeneri</t>
   </si>
   <si>
-    <t>Muhammad Sanusi Md Nor|link=Muhammad Sanusi Md Nor}}</t>
+    <t>Muhammad Sanusi Md Nor</t>
   </si>
   <si>
     <t>Padang Chichak;Kampung Betong;Kota Bukit;Kuala Jeneri;Kampung Kalai;Kampung Kuala Bigia;Kampung Chemara;Kampung Bigia;Kampung Telui;Batu Lima;Charok Padang;Hujong Bandar;Kampung Bandar;Tupai;FELDA Telui Timor;Beris Jaya</t>
@@ -3333,7 +3333,7 @@
     <t>Kupang</t>
   </si>
   <si>
-    <t>Najmi Ahmad|link=Najmi Ahmad}}</t>
+    <t>Najmi Ahmad</t>
   </si>
   <si>
     <t>Charok Salang;Kampung Asam Jawa;Charok Kelian;Sungai Limau;Charok Bemban;Gua Reban;Kampung Padang;Lanai;Mengkuang;Lubok Kabu;Kuala Pegang;Kampung Raja Kampung Landak;Pekan Kupang;Kuala Chenerai;Ketemba;Kampung Sadek;Bukit Terabak;Simpang Jerai;Kampung Tanjong;Ladang Sungai Tawar;Badenoch;Ulu Bakai;Pekan Malau;Badang;Kampung Sidim</t>
@@ -3357,7 +3357,7 @@
     <t>Merbau Pulas</t>
   </si>
   <si>
-    <t>Siti Ashah Ghazali|link=Siti Ashah Ghazali}}</t>
+    <t>Siti Ashah Ghazali</t>
   </si>
   <si>
     <t>Guar Lobak;Sidam Kanan;Kuala Sedim;Pekan Merbau Pulas;Kampung Jemerli;Bagan Sena;Sungai Karangan;Padang Meiha;Ladang Padang Meiha;Batu Puteh;Bukit Sedim;Kampung Bikan;Kampung Jangkang;Sungai Kob;Kampung Sungai Ular;Kulim High Tech;Padang China;Taman Perak;Taman Senangin;Kampung Baru;Jalan Serdang</t>
@@ -4116,7 +4116,7 @@
     <t>Penaga</t>
   </si>
   <si>
-    <t>Mohd Yusni Mat Piah|link=Mohd Yusni Mat Piah}}</t>
+    <t>Mohd Yusni Mat Piah</t>
   </si>
   <si>
     <t>Kuala Muda;Pulau Mertajam;Pasir Gebu;Penaga;Kota Aur;Permatang Janggus;Guar Kepah;Permatang Tiga Ringgit;Lahar Kepar</t>
@@ -5421,7 +5421,7 @@
     <t>Sabak</t>
   </si>
   <si>
-    <t>Sallehen Mukhyi|link=Sallehen Mukhyi}}</t>
+    <t>Sallehen Mukhyi</t>
   </si>
   <si>
     <t>Sabak Bernam Barat;Kampung Air Manis;Kampung Seri Aman;Tebuk Pulai;Torkington;Sabak Bernam Timur;Bagan Nira;Kampung Sapintas;Kampung Bagan Terap;Bagan Terap Parit Sembilan;Tebuk Kenchong;Parit Enam;Parit Dua Timur;Parit Tiga &amp; Empat;Parit Satu Barat;Sungai Lias;Batu 4 Sapintas</t>
@@ -5562,7 +5562,7 @@
     <t>Hulu Kelang</t>
   </si>
   <si>
-    <t>Mohamed Azmin Ali|link=Mohamed Azmin Ali}}</t>
+    <t>Mohamed Azmin Ali</t>
   </si>
   <si>
     <t>Bandar Melawati;Kelang Gate;Taman Melawati;Kemensah;Hulu Kelang;Taman Permata;Keramat Tengah AU 4;AU3 Rumah Teres;Sri Keramat AU 2A;Keramat AU 1;Keramat Pangsa;Melawati Jalan F &amp; H;Lembah Keramat AU 5C;Desa Keramat AU 2B &amp; AU 2C;Lembah Keramat AU 5D;Keramat AU 1B;AU3 Rumah Pangsa;Melawati Jalan G.E.C;Enggang Utara;Enggang Selatan</t>
@@ -5697,7 +5697,7 @@
     <t>Taman Medan</t>
   </si>
   <si>
-    <t>Afif Bahardin|link=Afif Bahardin}}</t>
+    <t>Afif Bahardin</t>
   </si>
   <si>
     <t>Seksyen 51;Seksyen 4 Petaling Jaya;Kawasan Melayu;PJS 1;Medan Pejasa;Taman Dato Harun 1;Taman Dato Harun 2;PJS 3;PJS 4;Baiduri;Petaling Utama;PJS 2;PJS 2C/12;PJS 2D;Kampung Medan;PJS 2C</t>
@@ -5796,7 +5796,7 @@
     <t>Selat Klang</t>
   </si>
   <si>
-    <t>Abdul Rashid Asari|link=Abdul Rashid Asari}}</t>
+    <t>Abdul Rashid Asari</t>
   </si>
   <si>
     <t>Sungai Udang Utara;Jalan Yadi;Kampong Delek;Sungai Sirih;Kuala Klang;Sri Perantau;Tanjong Klang;Sungai Lima;Bandar Pulau Ketam;Bagan Teo Chew;Sungai Udang Selatan;Kampong Delek Kanan;Kampong Delek Kiri;Bandar Sultan Sulaiman;Kampung Raja Uda Timur;Kampung Raja Uda Barat</t>
@@ -5859,9 +5859,6 @@
     <t>Sijangkang</t>
   </si>
   <si>
-    <t>Ahmad Yunus Hairi|link=Ahmad Yunus Hairi}}</t>
-  </si>
-  <si>
     <t>Sijangkang Utara;Sijangkang Dalam Utara;Sijangkang Dalam Selatan;Sijangkang Selatan;Batu 9 Kebun Baharu;Teluk 1;Ladang Carey Barat;Ladang Carey Selatan;Ladang Carey Timur;Teluk 2;Sungai Bumbun;Batu 10 Kebun Baharu;Sijangkang Jaya;Taman Panglima;Bukit Kemandul;Seri Cheeding;Bukit Cheeding (A);Kampung Jenjarum;Bandar Saujana Putra</t>
   </si>
   <si>
@@ -6429,7 +6426,7 @@
     <t>Bemban</t>
   </si>
   <si>
-    <t>Mohd Yadzil Yaakub|link=Mohd Yadzil Yaakub}}</t>
+    <t>Mohd Yadzil Yaakub</t>
   </si>
   <si>
     <t>Pondok Kempas;Ayer Kangkong;Kesang Tua;Kesang Jaya;Ayer Barok;Taman Maju;Ayer Panas;Seri Bemban;Tehel</t>
@@ -30576,7 +30573,7 @@
         <v>1947</v>
       </c>
       <c r="H321" t="s" s="7">
-        <v>1948</v>
+        <v>487</v>
       </c>
       <c r="I321" t="s" s="7">
         <v>26</v>
@@ -30590,7 +30587,7 @@
       <c r="N321" s="9"/>
       <c r="O321" s="9"/>
       <c r="P321" t="s" s="7">
-        <v>1949</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="322" ht="15.35" customHeight="1">
@@ -30613,10 +30610,10 @@
         <v>1641</v>
       </c>
       <c r="G322" t="s" s="7">
+        <v>1949</v>
+      </c>
+      <c r="H322" t="s" s="7">
         <v>1950</v>
-      </c>
-      <c r="H322" t="s" s="7">
-        <v>1951</v>
       </c>
       <c r="I322" t="s" s="7">
         <v>204</v>
@@ -30630,7 +30627,7 @@
       <c r="N322" s="9"/>
       <c r="O322" s="9"/>
       <c r="P322" t="s" s="7">
-        <v>1952</v>
+        <v>1951</v>
       </c>
     </row>
     <row r="323" ht="15.35" customHeight="1">
@@ -30653,10 +30650,10 @@
         <v>1645</v>
       </c>
       <c r="G323" t="s" s="7">
+        <v>1952</v>
+      </c>
+      <c r="H323" t="s" s="7">
         <v>1953</v>
-      </c>
-      <c r="H323" t="s" s="7">
-        <v>1954</v>
       </c>
       <c r="I323" t="s" s="7">
         <v>32</v>
@@ -30670,7 +30667,7 @@
       <c r="N323" s="9"/>
       <c r="O323" s="9"/>
       <c r="P323" t="s" s="7">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="324" ht="15.35" customHeight="1">
@@ -30693,10 +30690,10 @@
         <v>1649</v>
       </c>
       <c r="G324" t="s" s="7">
+        <v>1955</v>
+      </c>
+      <c r="H324" t="s" s="7">
         <v>1956</v>
-      </c>
-      <c r="H324" t="s" s="7">
-        <v>1957</v>
       </c>
       <c r="I324" t="s" s="7">
         <v>87</v>
@@ -30710,7 +30707,7 @@
       <c r="N324" s="9"/>
       <c r="O324" s="9"/>
       <c r="P324" t="s" s="7">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="325" ht="15.35" customHeight="1">
@@ -30733,10 +30730,10 @@
         <v>1653</v>
       </c>
       <c r="G325" t="s" s="7">
+        <v>1958</v>
+      </c>
+      <c r="H325" t="s" s="7">
         <v>1959</v>
-      </c>
-      <c r="H325" t="s" s="7">
-        <v>1960</v>
       </c>
       <c r="I325" t="s" s="7">
         <v>32</v>
@@ -30750,7 +30747,7 @@
       <c r="N325" s="9"/>
       <c r="O325" s="9"/>
       <c r="P325" t="s" s="7">
-        <v>1961</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="326" ht="15.35" customHeight="1">
@@ -30773,10 +30770,10 @@
         <v>1657</v>
       </c>
       <c r="G326" t="s" s="7">
+        <v>1961</v>
+      </c>
+      <c r="H326" t="s" s="7">
         <v>1962</v>
-      </c>
-      <c r="H326" t="s" s="7">
-        <v>1963</v>
       </c>
       <c r="I326" t="s" s="7">
         <v>204</v>
@@ -30790,7 +30787,7 @@
       <c r="N326" s="9"/>
       <c r="O326" s="9"/>
       <c r="P326" t="s" s="7">
-        <v>1964</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="327" ht="15.35" customHeight="1">
@@ -30813,7 +30810,7 @@
         <v>940</v>
       </c>
       <c r="G327" t="s" s="7">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H327" t="s" s="7">
         <v>542</v>
@@ -30830,7 +30827,7 @@
       <c r="N327" s="9"/>
       <c r="O327" s="9"/>
       <c r="P327" t="s" s="7">
-        <v>1966</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="328" ht="15.35" customHeight="1">
@@ -30853,7 +30850,7 @@
         <v>944</v>
       </c>
       <c r="G328" t="s" s="7">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H328" t="s" s="7">
         <v>534</v>
@@ -30870,7 +30867,7 @@
       <c r="N328" s="9"/>
       <c r="O328" s="9"/>
       <c r="P328" t="s" s="7">
-        <v>1968</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="329" ht="15.35" customHeight="1">
@@ -30893,10 +30890,10 @@
         <v>948</v>
       </c>
       <c r="G329" t="s" s="7">
+        <v>1968</v>
+      </c>
+      <c r="H329" t="s" s="7">
         <v>1969</v>
-      </c>
-      <c r="H329" t="s" s="7">
-        <v>1970</v>
       </c>
       <c r="I329" t="s" s="7">
         <v>254</v>
@@ -30910,7 +30907,7 @@
       <c r="N329" s="9"/>
       <c r="O329" s="9"/>
       <c r="P329" t="s" s="7">
-        <v>1971</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="330" ht="15.35" customHeight="1">
@@ -30933,10 +30930,10 @@
         <v>952</v>
       </c>
       <c r="G330" t="s" s="7">
+        <v>1971</v>
+      </c>
+      <c r="H330" t="s" s="7">
         <v>1972</v>
-      </c>
-      <c r="H330" t="s" s="7">
-        <v>1973</v>
       </c>
       <c r="I330" t="s" s="7">
         <v>423</v>
@@ -30950,7 +30947,7 @@
       <c r="N330" s="9"/>
       <c r="O330" s="9"/>
       <c r="P330" t="s" s="7">
-        <v>1974</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="331" ht="15.35" customHeight="1">
@@ -30973,10 +30970,10 @@
         <v>956</v>
       </c>
       <c r="G331" t="s" s="7">
+        <v>1974</v>
+      </c>
+      <c r="H331" t="s" s="7">
         <v>1975</v>
-      </c>
-      <c r="H331" t="s" s="7">
-        <v>1976</v>
       </c>
       <c r="I331" t="s" s="7">
         <v>26</v>
@@ -30990,7 +30987,7 @@
       <c r="N331" s="9"/>
       <c r="O331" s="9"/>
       <c r="P331" t="s" s="7">
-        <v>1977</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="332" ht="15.35" customHeight="1">
@@ -31013,10 +31010,10 @@
         <v>960</v>
       </c>
       <c r="G332" t="s" s="7">
+        <v>1977</v>
+      </c>
+      <c r="H332" t="s" s="7">
         <v>1978</v>
-      </c>
-      <c r="H332" t="s" s="7">
-        <v>1979</v>
       </c>
       <c r="I332" t="s" s="7">
         <v>254</v>
@@ -31030,7 +31027,7 @@
       <c r="N332" s="9"/>
       <c r="O332" s="9"/>
       <c r="P332" t="s" s="7">
-        <v>1980</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="333" ht="15.35" customHeight="1">
@@ -31053,10 +31050,10 @@
         <v>964</v>
       </c>
       <c r="G333" t="s" s="7">
+        <v>1980</v>
+      </c>
+      <c r="H333" t="s" s="7">
         <v>1981</v>
-      </c>
-      <c r="H333" t="s" s="7">
-        <v>1982</v>
       </c>
       <c r="I333" t="s" s="7">
         <v>254</v>
@@ -31070,7 +31067,7 @@
       <c r="N333" s="9"/>
       <c r="O333" s="9"/>
       <c r="P333" t="s" s="7">
-        <v>1983</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="334" ht="15.35" customHeight="1">
@@ -31093,10 +31090,10 @@
         <v>968</v>
       </c>
       <c r="G334" t="s" s="7">
+        <v>1983</v>
+      </c>
+      <c r="H334" t="s" s="7">
         <v>1984</v>
-      </c>
-      <c r="H334" t="s" s="7">
-        <v>1985</v>
       </c>
       <c r="I334" t="s" s="7">
         <v>204</v>
@@ -31110,7 +31107,7 @@
       <c r="N334" s="9"/>
       <c r="O334" s="9"/>
       <c r="P334" t="s" s="7">
-        <v>1986</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="335" ht="15.35" customHeight="1">
@@ -31133,10 +31130,10 @@
         <v>972</v>
       </c>
       <c r="G335" t="s" s="7">
+        <v>1986</v>
+      </c>
+      <c r="H335" t="s" s="7">
         <v>1987</v>
-      </c>
-      <c r="H335" t="s" s="7">
-        <v>1988</v>
       </c>
       <c r="I335" t="s" s="7">
         <v>254</v>
@@ -31150,7 +31147,7 @@
       <c r="N335" s="9"/>
       <c r="O335" s="9"/>
       <c r="P335" t="s" s="7">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="336" ht="15.35" customHeight="1">
@@ -31173,10 +31170,10 @@
         <v>976</v>
       </c>
       <c r="G336" t="s" s="7">
+        <v>1989</v>
+      </c>
+      <c r="H336" t="s" s="7">
         <v>1990</v>
-      </c>
-      <c r="H336" t="s" s="7">
-        <v>1991</v>
       </c>
       <c r="I336" t="s" s="7">
         <v>204</v>
@@ -31190,7 +31187,7 @@
       <c r="N336" s="9"/>
       <c r="O336" s="9"/>
       <c r="P336" t="s" s="7">
-        <v>1992</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="337" ht="15.35" customHeight="1">
@@ -31213,10 +31210,10 @@
         <v>980</v>
       </c>
       <c r="G337" t="s" s="7">
+        <v>1992</v>
+      </c>
+      <c r="H337" t="s" s="7">
         <v>1993</v>
-      </c>
-      <c r="H337" t="s" s="7">
-        <v>1994</v>
       </c>
       <c r="I337" t="s" s="7">
         <v>204</v>
@@ -31230,7 +31227,7 @@
       <c r="N337" s="9"/>
       <c r="O337" s="9"/>
       <c r="P337" t="s" s="7">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="338" ht="15.35" customHeight="1">
@@ -31253,10 +31250,10 @@
         <v>984</v>
       </c>
       <c r="G338" t="s" s="7">
+        <v>1995</v>
+      </c>
+      <c r="H338" t="s" s="7">
         <v>1996</v>
-      </c>
-      <c r="H338" t="s" s="7">
-        <v>1997</v>
       </c>
       <c r="I338" t="s" s="7">
         <v>204</v>
@@ -31270,7 +31267,7 @@
       <c r="N338" s="9"/>
       <c r="O338" s="9"/>
       <c r="P338" t="s" s="7">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="339" ht="15.35" customHeight="1">
@@ -31293,7 +31290,7 @@
         <v>988</v>
       </c>
       <c r="G339" t="s" s="7">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H339" t="s" s="7">
         <v>558</v>
@@ -31310,7 +31307,7 @@
       <c r="N339" s="9"/>
       <c r="O339" s="9"/>
       <c r="P339" t="s" s="7">
-        <v>2000</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="340" ht="15.35" customHeight="1">
@@ -31333,10 +31330,10 @@
         <v>992</v>
       </c>
       <c r="G340" t="s" s="7">
+        <v>2000</v>
+      </c>
+      <c r="H340" t="s" s="7">
         <v>2001</v>
-      </c>
-      <c r="H340" t="s" s="7">
-        <v>2002</v>
       </c>
       <c r="I340" t="s" s="7">
         <v>87</v>
@@ -31350,7 +31347,7 @@
       <c r="N340" s="9"/>
       <c r="O340" s="9"/>
       <c r="P340" t="s" s="7">
-        <v>2003</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="341" ht="15.35" customHeight="1">
@@ -31373,10 +31370,10 @@
         <v>996</v>
       </c>
       <c r="G341" t="s" s="7">
+        <v>2003</v>
+      </c>
+      <c r="H341" t="s" s="7">
         <v>2004</v>
-      </c>
-      <c r="H341" t="s" s="7">
-        <v>2005</v>
       </c>
       <c r="I341" t="s" s="7">
         <v>254</v>
@@ -31390,7 +31387,7 @@
       <c r="N341" s="9"/>
       <c r="O341" s="9"/>
       <c r="P341" t="s" s="7">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="342" ht="15.35" customHeight="1">
@@ -31413,10 +31410,10 @@
         <v>1044</v>
       </c>
       <c r="G342" t="s" s="7">
+        <v>2006</v>
+      </c>
+      <c r="H342" t="s" s="7">
         <v>2007</v>
-      </c>
-      <c r="H342" t="s" s="7">
-        <v>2008</v>
       </c>
       <c r="I342" t="s" s="7">
         <v>254</v>
@@ -31430,7 +31427,7 @@
       <c r="N342" s="9"/>
       <c r="O342" s="9"/>
       <c r="P342" t="s" s="7">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="343" ht="15.35" customHeight="1">
@@ -31453,10 +31450,10 @@
         <v>1048</v>
       </c>
       <c r="G343" t="s" s="7">
+        <v>2009</v>
+      </c>
+      <c r="H343" t="s" s="7">
         <v>2010</v>
-      </c>
-      <c r="H343" t="s" s="7">
-        <v>2011</v>
       </c>
       <c r="I343" t="s" s="7">
         <v>254</v>
@@ -31470,7 +31467,7 @@
       <c r="N343" s="9"/>
       <c r="O343" s="9"/>
       <c r="P343" t="s" s="7">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="344" ht="15.35" customHeight="1">
@@ -31493,10 +31490,10 @@
         <v>1052</v>
       </c>
       <c r="G344" t="s" s="7">
+        <v>2012</v>
+      </c>
+      <c r="H344" t="s" s="7">
         <v>2013</v>
-      </c>
-      <c r="H344" t="s" s="7">
-        <v>2014</v>
       </c>
       <c r="I344" t="s" s="7">
         <v>87</v>
@@ -31510,7 +31507,7 @@
       <c r="N344" s="9"/>
       <c r="O344" s="9"/>
       <c r="P344" t="s" s="7">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="345" ht="15.35" customHeight="1">
@@ -31533,10 +31530,10 @@
         <v>1056</v>
       </c>
       <c r="G345" t="s" s="7">
+        <v>2015</v>
+      </c>
+      <c r="H345" t="s" s="7">
         <v>2016</v>
-      </c>
-      <c r="H345" t="s" s="7">
-        <v>2017</v>
       </c>
       <c r="I345" t="s" s="7">
         <v>254</v>
@@ -31550,7 +31547,7 @@
       <c r="N345" s="9"/>
       <c r="O345" s="9"/>
       <c r="P345" t="s" s="7">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="346" ht="15.35" customHeight="1">
@@ -31573,10 +31570,10 @@
         <v>1060</v>
       </c>
       <c r="G346" t="s" s="7">
+        <v>2018</v>
+      </c>
+      <c r="H346" t="s" s="7">
         <v>2019</v>
-      </c>
-      <c r="H346" t="s" s="7">
-        <v>2020</v>
       </c>
       <c r="I346" t="s" s="7">
         <v>32</v>
@@ -31590,7 +31587,7 @@
       <c r="N346" s="9"/>
       <c r="O346" s="9"/>
       <c r="P346" t="s" s="7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="347" ht="15.35" customHeight="1">
@@ -31613,10 +31610,10 @@
         <v>1064</v>
       </c>
       <c r="G347" t="s" s="7">
+        <v>2021</v>
+      </c>
+      <c r="H347" t="s" s="7">
         <v>2022</v>
-      </c>
-      <c r="H347" t="s" s="7">
-        <v>2023</v>
       </c>
       <c r="I347" t="s" s="7">
         <v>204</v>
@@ -31630,7 +31627,7 @@
       <c r="N347" s="9"/>
       <c r="O347" s="9"/>
       <c r="P347" t="s" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="348" ht="15.35" customHeight="1">
@@ -31653,10 +31650,10 @@
         <v>1068</v>
       </c>
       <c r="G348" t="s" s="7">
+        <v>2024</v>
+      </c>
+      <c r="H348" t="s" s="7">
         <v>2025</v>
-      </c>
-      <c r="H348" t="s" s="7">
-        <v>2026</v>
       </c>
       <c r="I348" t="s" s="7">
         <v>204</v>
@@ -31670,7 +31667,7 @@
       <c r="N348" s="9"/>
       <c r="O348" s="9"/>
       <c r="P348" t="s" s="7">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="349" ht="15.35" customHeight="1">
@@ -31693,10 +31690,10 @@
         <v>1072</v>
       </c>
       <c r="G349" t="s" s="7">
+        <v>2027</v>
+      </c>
+      <c r="H349" t="s" s="7">
         <v>2028</v>
-      </c>
-      <c r="H349" t="s" s="7">
-        <v>2029</v>
       </c>
       <c r="I349" t="s" s="7">
         <v>204</v>
@@ -31710,7 +31707,7 @@
       <c r="N349" s="9"/>
       <c r="O349" s="9"/>
       <c r="P349" t="s" s="7">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="350" ht="15.35" customHeight="1">
@@ -31733,10 +31730,10 @@
         <v>1076</v>
       </c>
       <c r="G350" t="s" s="7">
+        <v>2030</v>
+      </c>
+      <c r="H350" t="s" s="7">
         <v>2031</v>
-      </c>
-      <c r="H350" t="s" s="7">
-        <v>2032</v>
       </c>
       <c r="I350" t="s" s="7">
         <v>204</v>
@@ -31750,7 +31747,7 @@
       <c r="N350" s="9"/>
       <c r="O350" s="9"/>
       <c r="P350" t="s" s="7">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="351" ht="15.35" customHeight="1">
@@ -31773,10 +31770,10 @@
         <v>1080</v>
       </c>
       <c r="G351" t="s" s="7">
+        <v>2033</v>
+      </c>
+      <c r="H351" t="s" s="7">
         <v>2034</v>
-      </c>
-      <c r="H351" t="s" s="7">
-        <v>2035</v>
       </c>
       <c r="I351" t="s" s="7">
         <v>26</v>
@@ -31790,7 +31787,7 @@
       <c r="N351" s="9"/>
       <c r="O351" s="9"/>
       <c r="P351" t="s" s="7">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="352" ht="15.35" customHeight="1">
@@ -31813,10 +31810,10 @@
         <v>1084</v>
       </c>
       <c r="G352" t="s" s="7">
+        <v>2036</v>
+      </c>
+      <c r="H352" t="s" s="7">
         <v>2037</v>
-      </c>
-      <c r="H352" t="s" s="7">
-        <v>2038</v>
       </c>
       <c r="I352" t="s" s="7">
         <v>254</v>
@@ -31830,7 +31827,7 @@
       <c r="N352" s="9"/>
       <c r="O352" s="9"/>
       <c r="P352" t="s" s="7">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="353" ht="15.35" customHeight="1">
@@ -31853,7 +31850,7 @@
         <v>1088</v>
       </c>
       <c r="G353" t="s" s="7">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="H353" t="s" s="7">
         <v>554</v>
@@ -31870,7 +31867,7 @@
       <c r="N353" s="9"/>
       <c r="O353" s="9"/>
       <c r="P353" t="s" s="7">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="354" ht="15.35" customHeight="1">
@@ -31893,10 +31890,10 @@
         <v>1092</v>
       </c>
       <c r="G354" t="s" s="7">
+        <v>2041</v>
+      </c>
+      <c r="H354" t="s" s="7">
         <v>2042</v>
-      </c>
-      <c r="H354" t="s" s="7">
-        <v>2043</v>
       </c>
       <c r="I354" t="s" s="7">
         <v>254</v>
@@ -31910,7 +31907,7 @@
       <c r="N354" s="9"/>
       <c r="O354" s="9"/>
       <c r="P354" t="s" s="7">
-        <v>2044</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="355" ht="15.35" customHeight="1">
@@ -31933,10 +31930,10 @@
         <v>1096</v>
       </c>
       <c r="G355" t="s" s="7">
+        <v>2044</v>
+      </c>
+      <c r="H355" t="s" s="7">
         <v>2045</v>
-      </c>
-      <c r="H355" t="s" s="7">
-        <v>2046</v>
       </c>
       <c r="I355" t="s" s="7">
         <v>87</v>
@@ -31950,7 +31947,7 @@
       <c r="N355" s="9"/>
       <c r="O355" s="9"/>
       <c r="P355" t="s" s="7">
-        <v>2047</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="356" ht="15.35" customHeight="1">
@@ -31973,10 +31970,10 @@
         <v>1100</v>
       </c>
       <c r="G356" t="s" s="7">
+        <v>2047</v>
+      </c>
+      <c r="H356" t="s" s="7">
         <v>2048</v>
-      </c>
-      <c r="H356" t="s" s="7">
-        <v>2049</v>
       </c>
       <c r="I356" t="s" s="7">
         <v>204</v>
@@ -31990,7 +31987,7 @@
       <c r="N356" s="9"/>
       <c r="O356" s="9"/>
       <c r="P356" t="s" s="7">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="357" ht="15.35" customHeight="1">
@@ -32013,10 +32010,10 @@
         <v>1104</v>
       </c>
       <c r="G357" t="s" s="7">
+        <v>2050</v>
+      </c>
+      <c r="H357" t="s" s="7">
         <v>2051</v>
-      </c>
-      <c r="H357" t="s" s="7">
-        <v>2052</v>
       </c>
       <c r="I357" t="s" s="7">
         <v>26</v>
@@ -32030,7 +32027,7 @@
       <c r="N357" s="9"/>
       <c r="O357" s="9"/>
       <c r="P357" t="s" s="7">
-        <v>2053</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="358" ht="15.35" customHeight="1">
@@ -32053,10 +32050,10 @@
         <v>1108</v>
       </c>
       <c r="G358" t="s" s="7">
+        <v>2053</v>
+      </c>
+      <c r="H358" t="s" s="7">
         <v>2054</v>
-      </c>
-      <c r="H358" t="s" s="7">
-        <v>2055</v>
       </c>
       <c r="I358" t="s" s="7">
         <v>254</v>
@@ -32070,7 +32067,7 @@
       <c r="N358" s="9"/>
       <c r="O358" s="9"/>
       <c r="P358" t="s" s="7">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="359" ht="15.35" customHeight="1">
@@ -32093,10 +32090,10 @@
         <v>1112</v>
       </c>
       <c r="G359" t="s" s="7">
+        <v>2056</v>
+      </c>
+      <c r="H359" t="s" s="7">
         <v>2057</v>
-      </c>
-      <c r="H359" t="s" s="7">
-        <v>2058</v>
       </c>
       <c r="I359" t="s" s="7">
         <v>87</v>
@@ -32110,7 +32107,7 @@
       <c r="N359" s="9"/>
       <c r="O359" s="9"/>
       <c r="P359" t="s" s="7">
-        <v>2059</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="360" ht="15.35" customHeight="1">
@@ -32133,10 +32130,10 @@
         <v>1116</v>
       </c>
       <c r="G360" t="s" s="7">
+        <v>2059</v>
+      </c>
+      <c r="H360" t="s" s="7">
         <v>2060</v>
-      </c>
-      <c r="H360" t="s" s="7">
-        <v>2061</v>
       </c>
       <c r="I360" t="s" s="7">
         <v>32</v>
@@ -32150,7 +32147,7 @@
       <c r="N360" s="9"/>
       <c r="O360" s="9"/>
       <c r="P360" t="s" s="7">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="361" ht="15.35" customHeight="1">
@@ -32173,10 +32170,10 @@
         <v>1120</v>
       </c>
       <c r="G361" t="s" s="7">
+        <v>2062</v>
+      </c>
+      <c r="H361" t="s" s="7">
         <v>2063</v>
-      </c>
-      <c r="H361" t="s" s="7">
-        <v>2064</v>
       </c>
       <c r="I361" t="s" s="7">
         <v>254</v>
@@ -32190,7 +32187,7 @@
       <c r="N361" s="9"/>
       <c r="O361" s="9"/>
       <c r="P361" t="s" s="7">
-        <v>2065</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="362" ht="15.35" customHeight="1">
@@ -32213,10 +32210,10 @@
         <v>1125</v>
       </c>
       <c r="G362" t="s" s="7">
+        <v>2065</v>
+      </c>
+      <c r="H362" t="s" s="7">
         <v>2066</v>
-      </c>
-      <c r="H362" t="s" s="7">
-        <v>2067</v>
       </c>
       <c r="I362" t="s" s="7">
         <v>204</v>
@@ -32230,7 +32227,7 @@
       <c r="N362" s="9"/>
       <c r="O362" s="9"/>
       <c r="P362" t="s" s="7">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="363" ht="15.35" customHeight="1">
@@ -32253,10 +32250,10 @@
         <v>940</v>
       </c>
       <c r="G363" t="s" s="7">
+        <v>2068</v>
+      </c>
+      <c r="H363" t="s" s="7">
         <v>2069</v>
-      </c>
-      <c r="H363" t="s" s="7">
-        <v>2070</v>
       </c>
       <c r="I363" t="s" s="7">
         <v>254</v>
@@ -32270,7 +32267,7 @@
       <c r="N363" s="9"/>
       <c r="O363" s="9"/>
       <c r="P363" t="s" s="7">
-        <v>2071</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="364" ht="15.35" customHeight="1">
@@ -32293,10 +32290,10 @@
         <v>944</v>
       </c>
       <c r="G364" t="s" s="7">
+        <v>2071</v>
+      </c>
+      <c r="H364" t="s" s="7">
         <v>2072</v>
-      </c>
-      <c r="H364" t="s" s="7">
-        <v>2073</v>
       </c>
       <c r="I364" t="s" s="7">
         <v>254</v>
@@ -32310,7 +32307,7 @@
       <c r="N364" s="9"/>
       <c r="O364" s="9"/>
       <c r="P364" t="s" s="7">
-        <v>2074</v>
+        <v>2073</v>
       </c>
     </row>
     <row r="365" ht="15.35" customHeight="1">
@@ -32333,10 +32330,10 @@
         <v>948</v>
       </c>
       <c r="G365" t="s" s="7">
+        <v>2074</v>
+      </c>
+      <c r="H365" t="s" s="7">
         <v>2075</v>
-      </c>
-      <c r="H365" t="s" s="7">
-        <v>2076</v>
       </c>
       <c r="I365" t="s" s="7">
         <v>254</v>
@@ -32350,7 +32347,7 @@
       <c r="N365" s="9"/>
       <c r="O365" s="9"/>
       <c r="P365" t="s" s="7">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="366" ht="15.35" customHeight="1">
@@ -32373,10 +32370,10 @@
         <v>952</v>
       </c>
       <c r="G366" t="s" s="7">
+        <v>2077</v>
+      </c>
+      <c r="H366" t="s" s="7">
         <v>2078</v>
-      </c>
-      <c r="H366" t="s" s="7">
-        <v>2079</v>
       </c>
       <c r="I366" t="s" s="7">
         <v>254</v>
@@ -32390,7 +32387,7 @@
       <c r="N366" s="9"/>
       <c r="O366" s="9"/>
       <c r="P366" t="s" s="7">
-        <v>2080</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="367" ht="15.35" customHeight="1">
@@ -32413,10 +32410,10 @@
         <v>956</v>
       </c>
       <c r="G367" t="s" s="7">
+        <v>2080</v>
+      </c>
+      <c r="H367" t="s" s="7">
         <v>2081</v>
-      </c>
-      <c r="H367" t="s" s="7">
-        <v>2082</v>
       </c>
       <c r="I367" t="s" s="7">
         <v>254</v>
@@ -32430,7 +32427,7 @@
       <c r="N367" s="9"/>
       <c r="O367" s="9"/>
       <c r="P367" t="s" s="7">
-        <v>2083</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="368" ht="15.35" customHeight="1">
@@ -32453,10 +32450,10 @@
         <v>960</v>
       </c>
       <c r="G368" t="s" s="7">
+        <v>2083</v>
+      </c>
+      <c r="H368" t="s" s="7">
         <v>2084</v>
-      </c>
-      <c r="H368" t="s" s="7">
-        <v>2085</v>
       </c>
       <c r="I368" t="s" s="7">
         <v>254</v>
@@ -32470,7 +32467,7 @@
       <c r="N368" s="9"/>
       <c r="O368" s="9"/>
       <c r="P368" t="s" s="7">
-        <v>2086</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="369" ht="15.35" customHeight="1">
@@ -32493,10 +32490,10 @@
         <v>964</v>
       </c>
       <c r="G369" t="s" s="7">
+        <v>2086</v>
+      </c>
+      <c r="H369" t="s" s="7">
         <v>2087</v>
-      </c>
-      <c r="H369" t="s" s="7">
-        <v>2088</v>
       </c>
       <c r="I369" t="s" s="7">
         <v>324</v>
@@ -32510,7 +32507,7 @@
       <c r="N369" s="9"/>
       <c r="O369" s="9"/>
       <c r="P369" t="s" s="7">
-        <v>2089</v>
+        <v>2088</v>
       </c>
     </row>
     <row r="370" ht="15.35" customHeight="1">
@@ -32533,10 +32530,10 @@
         <v>968</v>
       </c>
       <c r="G370" t="s" s="7">
+        <v>2089</v>
+      </c>
+      <c r="H370" t="s" s="7">
         <v>2090</v>
-      </c>
-      <c r="H370" t="s" s="7">
-        <v>2091</v>
       </c>
       <c r="I370" t="s" s="7">
         <v>626</v>
@@ -32550,7 +32547,7 @@
       <c r="N370" s="9"/>
       <c r="O370" s="9"/>
       <c r="P370" t="s" s="7">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="371" ht="15.35" customHeight="1">
@@ -32573,10 +32570,10 @@
         <v>972</v>
       </c>
       <c r="G371" t="s" s="7">
+        <v>2092</v>
+      </c>
+      <c r="H371" t="s" s="7">
         <v>2093</v>
-      </c>
-      <c r="H371" t="s" s="7">
-        <v>2094</v>
       </c>
       <c r="I371" t="s" s="7">
         <v>254</v>
@@ -32590,7 +32587,7 @@
       <c r="N371" s="9"/>
       <c r="O371" s="9"/>
       <c r="P371" t="s" s="7">
-        <v>2095</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="372" ht="15.35" customHeight="1">
@@ -32613,10 +32610,10 @@
         <v>976</v>
       </c>
       <c r="G372" t="s" s="7">
+        <v>2095</v>
+      </c>
+      <c r="H372" t="s" s="7">
         <v>2096</v>
-      </c>
-      <c r="H372" t="s" s="7">
-        <v>2097</v>
       </c>
       <c r="I372" t="s" s="7">
         <v>254</v>
@@ -32630,7 +32627,7 @@
       <c r="N372" s="9"/>
       <c r="O372" s="9"/>
       <c r="P372" t="s" s="7">
-        <v>2098</v>
+        <v>2097</v>
       </c>
     </row>
     <row r="373" ht="15.35" customHeight="1">
@@ -32653,10 +32650,10 @@
         <v>980</v>
       </c>
       <c r="G373" t="s" s="7">
+        <v>2098</v>
+      </c>
+      <c r="H373" t="s" s="7">
         <v>2099</v>
-      </c>
-      <c r="H373" t="s" s="7">
-        <v>2100</v>
       </c>
       <c r="I373" t="s" s="7">
         <v>32</v>
@@ -32670,7 +32667,7 @@
       <c r="N373" s="9"/>
       <c r="O373" s="9"/>
       <c r="P373" t="s" s="7">
-        <v>2101</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="374" ht="15.35" customHeight="1">
@@ -32693,10 +32690,10 @@
         <v>984</v>
       </c>
       <c r="G374" t="s" s="7">
+        <v>2101</v>
+      </c>
+      <c r="H374" t="s" s="7">
         <v>2102</v>
-      </c>
-      <c r="H374" t="s" s="7">
-        <v>2103</v>
       </c>
       <c r="I374" t="s" s="7">
         <v>254</v>
@@ -32710,7 +32707,7 @@
       <c r="N374" s="9"/>
       <c r="O374" s="9"/>
       <c r="P374" t="s" s="7">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="375" ht="15.35" customHeight="1">
@@ -32733,10 +32730,10 @@
         <v>988</v>
       </c>
       <c r="G375" t="s" s="7">
+        <v>2104</v>
+      </c>
+      <c r="H375" t="s" s="7">
         <v>2105</v>
-      </c>
-      <c r="H375" t="s" s="7">
-        <v>2106</v>
       </c>
       <c r="I375" t="s" s="7">
         <v>254</v>
@@ -32750,7 +32747,7 @@
       <c r="N375" s="9"/>
       <c r="O375" s="9"/>
       <c r="P375" t="s" s="7">
-        <v>2107</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="376" ht="15.35" customHeight="1">
@@ -32773,10 +32770,10 @@
         <v>992</v>
       </c>
       <c r="G376" t="s" s="7">
+        <v>2107</v>
+      </c>
+      <c r="H376" t="s" s="7">
         <v>2108</v>
-      </c>
-      <c r="H376" t="s" s="7">
-        <v>2109</v>
       </c>
       <c r="I376" t="s" s="7">
         <v>626</v>
@@ -32790,7 +32787,7 @@
       <c r="N376" s="9"/>
       <c r="O376" s="9"/>
       <c r="P376" t="s" s="7">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="377" ht="15.35" customHeight="1">
@@ -32813,10 +32810,10 @@
         <v>996</v>
       </c>
       <c r="G377" t="s" s="7">
+        <v>2110</v>
+      </c>
+      <c r="H377" t="s" s="7">
         <v>2111</v>
-      </c>
-      <c r="H377" t="s" s="7">
-        <v>2112</v>
       </c>
       <c r="I377" t="s" s="7">
         <v>254</v>
@@ -32830,7 +32827,7 @@
       <c r="N377" s="9"/>
       <c r="O377" s="9"/>
       <c r="P377" t="s" s="7">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="378" ht="15.35" customHeight="1">
@@ -32853,10 +32850,10 @@
         <v>1044</v>
       </c>
       <c r="G378" t="s" s="7">
+        <v>2113</v>
+      </c>
+      <c r="H378" t="s" s="7">
         <v>2114</v>
-      </c>
-      <c r="H378" t="s" s="7">
-        <v>2115</v>
       </c>
       <c r="I378" t="s" s="7">
         <v>204</v>
@@ -32870,7 +32867,7 @@
       <c r="N378" s="9"/>
       <c r="O378" s="9"/>
       <c r="P378" t="s" s="7">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="379" ht="15.35" customHeight="1">
@@ -32893,7 +32890,7 @@
         <v>1048</v>
       </c>
       <c r="G379" t="s" s="7">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="H379" t="s" s="7">
         <v>571</v>
@@ -32910,7 +32907,7 @@
       <c r="N379" s="9"/>
       <c r="O379" s="9"/>
       <c r="P379" t="s" s="7">
-        <v>2118</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="380" ht="15.35" customHeight="1">
@@ -32933,10 +32930,10 @@
         <v>1052</v>
       </c>
       <c r="G380" t="s" s="7">
+        <v>2118</v>
+      </c>
+      <c r="H380" t="s" s="7">
         <v>2119</v>
-      </c>
-      <c r="H380" t="s" s="7">
-        <v>2120</v>
       </c>
       <c r="I380" t="s" s="7">
         <v>254</v>
@@ -32950,7 +32947,7 @@
       <c r="N380" s="9"/>
       <c r="O380" s="9"/>
       <c r="P380" t="s" s="7">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="381" ht="15.35" customHeight="1">
@@ -32973,10 +32970,10 @@
         <v>1056</v>
       </c>
       <c r="G381" t="s" s="7">
+        <v>2121</v>
+      </c>
+      <c r="H381" t="s" s="7">
         <v>2122</v>
-      </c>
-      <c r="H381" t="s" s="7">
-        <v>2123</v>
       </c>
       <c r="I381" t="s" s="7">
         <v>204</v>
@@ -32990,7 +32987,7 @@
       <c r="N381" s="9"/>
       <c r="O381" s="9"/>
       <c r="P381" t="s" s="7">
-        <v>2124</v>
+        <v>2123</v>
       </c>
     </row>
     <row r="382" ht="15.35" customHeight="1">
@@ -33013,10 +33010,10 @@
         <v>1060</v>
       </c>
       <c r="G382" t="s" s="7">
+        <v>2124</v>
+      </c>
+      <c r="H382" t="s" s="7">
         <v>2125</v>
-      </c>
-      <c r="H382" t="s" s="7">
-        <v>2126</v>
       </c>
       <c r="I382" t="s" s="7">
         <v>204</v>
@@ -33030,7 +33027,7 @@
       <c r="N382" s="9"/>
       <c r="O382" s="9"/>
       <c r="P382" t="s" s="7">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="383" ht="15.35" customHeight="1">
@@ -33053,10 +33050,10 @@
         <v>1064</v>
       </c>
       <c r="G383" t="s" s="7">
+        <v>2127</v>
+      </c>
+      <c r="H383" t="s" s="7">
         <v>2128</v>
-      </c>
-      <c r="H383" t="s" s="7">
-        <v>2129</v>
       </c>
       <c r="I383" t="s" s="7">
         <v>254</v>
@@ -33070,7 +33067,7 @@
       <c r="N383" s="9"/>
       <c r="O383" s="9"/>
       <c r="P383" t="s" s="7">
-        <v>2130</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="384" ht="15.35" customHeight="1">
@@ -33093,10 +33090,10 @@
         <v>1068</v>
       </c>
       <c r="G384" t="s" s="7">
+        <v>2130</v>
+      </c>
+      <c r="H384" t="s" s="7">
         <v>2131</v>
-      </c>
-      <c r="H384" t="s" s="7">
-        <v>2132</v>
       </c>
       <c r="I384" t="s" s="7">
         <v>204</v>
@@ -33110,7 +33107,7 @@
       <c r="N384" s="9"/>
       <c r="O384" s="9"/>
       <c r="P384" t="s" s="7">
-        <v>2133</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="385" ht="15.35" customHeight="1">
@@ -33133,10 +33130,10 @@
         <v>1072</v>
       </c>
       <c r="G385" t="s" s="7">
+        <v>2133</v>
+      </c>
+      <c r="H385" t="s" s="7">
         <v>2134</v>
-      </c>
-      <c r="H385" t="s" s="7">
-        <v>2135</v>
       </c>
       <c r="I385" t="s" s="7">
         <v>254</v>
@@ -33150,7 +33147,7 @@
       <c r="N385" s="9"/>
       <c r="O385" s="9"/>
       <c r="P385" t="s" s="7">
-        <v>2136</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="386" ht="15.35" customHeight="1">
@@ -33173,10 +33170,10 @@
         <v>1076</v>
       </c>
       <c r="G386" t="s" s="7">
+        <v>2136</v>
+      </c>
+      <c r="H386" t="s" s="7">
         <v>2137</v>
-      </c>
-      <c r="H386" t="s" s="7">
-        <v>2138</v>
       </c>
       <c r="I386" t="s" s="7">
         <v>32</v>
@@ -33190,7 +33187,7 @@
       <c r="N386" s="9"/>
       <c r="O386" s="9"/>
       <c r="P386" t="s" s="7">
-        <v>2139</v>
+        <v>2138</v>
       </c>
     </row>
     <row r="387" ht="15.35" customHeight="1">
@@ -33213,10 +33210,10 @@
         <v>1080</v>
       </c>
       <c r="G387" t="s" s="7">
+        <v>2139</v>
+      </c>
+      <c r="H387" t="s" s="7">
         <v>2140</v>
-      </c>
-      <c r="H387" t="s" s="7">
-        <v>2141</v>
       </c>
       <c r="I387" t="s" s="7">
         <v>254</v>
@@ -33230,7 +33227,7 @@
       <c r="N387" s="9"/>
       <c r="O387" s="9"/>
       <c r="P387" t="s" s="7">
-        <v>2142</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="388" ht="15.35" customHeight="1">
@@ -33253,10 +33250,10 @@
         <v>1084</v>
       </c>
       <c r="G388" t="s" s="7">
+        <v>2142</v>
+      </c>
+      <c r="H388" t="s" s="7">
         <v>2143</v>
-      </c>
-      <c r="H388" t="s" s="7">
-        <v>2144</v>
       </c>
       <c r="I388" t="s" s="7">
         <v>254</v>
@@ -33270,7 +33267,7 @@
       <c r="N388" s="9"/>
       <c r="O388" s="9"/>
       <c r="P388" t="s" s="7">
-        <v>2145</v>
+        <v>2144</v>
       </c>
     </row>
     <row r="389" ht="15.35" customHeight="1">
@@ -33293,10 +33290,10 @@
         <v>1088</v>
       </c>
       <c r="G389" t="s" s="7">
+        <v>2145</v>
+      </c>
+      <c r="H389" t="s" s="7">
         <v>2146</v>
-      </c>
-      <c r="H389" t="s" s="7">
-        <v>2147</v>
       </c>
       <c r="I389" t="s" s="7">
         <v>254</v>
@@ -33310,7 +33307,7 @@
       <c r="N389" s="9"/>
       <c r="O389" s="9"/>
       <c r="P389" t="s" s="7">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="390" ht="15.35" customHeight="1">
@@ -33333,10 +33330,10 @@
         <v>1092</v>
       </c>
       <c r="G390" t="s" s="7">
+        <v>2148</v>
+      </c>
+      <c r="H390" t="s" s="7">
         <v>2149</v>
-      </c>
-      <c r="H390" t="s" s="7">
-        <v>2150</v>
       </c>
       <c r="I390" t="s" s="7">
         <v>254</v>
@@ -33350,7 +33347,7 @@
       <c r="N390" s="9"/>
       <c r="O390" s="9"/>
       <c r="P390" t="s" s="7">
-        <v>2151</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="391" ht="15.35" customHeight="1">
@@ -33373,10 +33370,10 @@
         <v>940</v>
       </c>
       <c r="G391" t="s" s="7">
+        <v>2151</v>
+      </c>
+      <c r="H391" t="s" s="7">
         <v>2152</v>
-      </c>
-      <c r="H391" t="s" s="7">
-        <v>2153</v>
       </c>
       <c r="I391" t="s" s="7">
         <v>254</v>
@@ -33390,7 +33387,7 @@
       <c r="N391" s="9"/>
       <c r="O391" s="9"/>
       <c r="P391" t="s" s="7">
-        <v>2154</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="392" ht="15.35" customHeight="1">
@@ -33413,10 +33410,10 @@
         <v>944</v>
       </c>
       <c r="G392" t="s" s="7">
+        <v>2154</v>
+      </c>
+      <c r="H392" t="s" s="7">
         <v>2155</v>
-      </c>
-      <c r="H392" t="s" s="7">
-        <v>2156</v>
       </c>
       <c r="I392" t="s" s="7">
         <v>204</v>
@@ -33430,7 +33427,7 @@
       <c r="N392" s="9"/>
       <c r="O392" s="9"/>
       <c r="P392" t="s" s="7">
-        <v>2157</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="393" ht="15.35" customHeight="1">
@@ -33453,10 +33450,10 @@
         <v>948</v>
       </c>
       <c r="G393" t="s" s="7">
+        <v>2157</v>
+      </c>
+      <c r="H393" t="s" s="7">
         <v>2158</v>
-      </c>
-      <c r="H393" t="s" s="7">
-        <v>2159</v>
       </c>
       <c r="I393" t="s" s="7">
         <v>254</v>
@@ -33470,7 +33467,7 @@
       <c r="N393" s="9"/>
       <c r="O393" s="9"/>
       <c r="P393" t="s" s="7">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="394" ht="15.35" customHeight="1">
@@ -33493,10 +33490,10 @@
         <v>952</v>
       </c>
       <c r="G394" t="s" s="7">
+        <v>2160</v>
+      </c>
+      <c r="H394" t="s" s="7">
         <v>2161</v>
-      </c>
-      <c r="H394" t="s" s="7">
-        <v>2162</v>
       </c>
       <c r="I394" t="s" s="7">
         <v>324</v>
@@ -33510,7 +33507,7 @@
       <c r="N394" s="9"/>
       <c r="O394" s="9"/>
       <c r="P394" t="s" s="7">
-        <v>2163</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="395" ht="15.35" customHeight="1">
@@ -33533,10 +33530,10 @@
         <v>956</v>
       </c>
       <c r="G395" t="s" s="7">
+        <v>2163</v>
+      </c>
+      <c r="H395" t="s" s="7">
         <v>2164</v>
-      </c>
-      <c r="H395" t="s" s="7">
-        <v>2165</v>
       </c>
       <c r="I395" t="s" s="7">
         <v>254</v>
@@ -33550,7 +33547,7 @@
       <c r="N395" s="9"/>
       <c r="O395" s="9"/>
       <c r="P395" t="s" s="7">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="396" ht="15.35" customHeight="1">
@@ -33573,10 +33570,10 @@
         <v>960</v>
       </c>
       <c r="G396" t="s" s="7">
+        <v>2166</v>
+      </c>
+      <c r="H396" t="s" s="7">
         <v>2167</v>
-      </c>
-      <c r="H396" t="s" s="7">
-        <v>2168</v>
       </c>
       <c r="I396" t="s" s="7">
         <v>626</v>
@@ -33590,7 +33587,7 @@
       <c r="N396" s="9"/>
       <c r="O396" s="9"/>
       <c r="P396" t="s" s="7">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="397" ht="15.35" customHeight="1">
@@ -33613,10 +33610,10 @@
         <v>964</v>
       </c>
       <c r="G397" t="s" s="7">
+        <v>2169</v>
+      </c>
+      <c r="H397" t="s" s="7">
         <v>2170</v>
-      </c>
-      <c r="H397" t="s" s="7">
-        <v>2171</v>
       </c>
       <c r="I397" t="s" s="7">
         <v>32</v>
@@ -33630,7 +33627,7 @@
       <c r="N397" s="9"/>
       <c r="O397" s="9"/>
       <c r="P397" t="s" s="7">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="398" ht="15.35" customHeight="1">
@@ -33653,10 +33650,10 @@
         <v>968</v>
       </c>
       <c r="G398" t="s" s="7">
+        <v>2172</v>
+      </c>
+      <c r="H398" t="s" s="7">
         <v>2173</v>
-      </c>
-      <c r="H398" t="s" s="7">
-        <v>2174</v>
       </c>
       <c r="I398" t="s" s="7">
         <v>254</v>
@@ -33670,7 +33667,7 @@
       <c r="N398" s="9"/>
       <c r="O398" s="9"/>
       <c r="P398" t="s" s="7">
-        <v>2175</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="399" ht="15.35" customHeight="1">
@@ -33693,10 +33690,10 @@
         <v>972</v>
       </c>
       <c r="G399" t="s" s="7">
+        <v>2175</v>
+      </c>
+      <c r="H399" t="s" s="7">
         <v>2176</v>
-      </c>
-      <c r="H399" t="s" s="7">
-        <v>2177</v>
       </c>
       <c r="I399" t="s" s="7">
         <v>254</v>
@@ -33710,7 +33707,7 @@
       <c r="N399" s="9"/>
       <c r="O399" s="9"/>
       <c r="P399" t="s" s="7">
-        <v>2178</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="400" ht="15.35" customHeight="1">
@@ -33733,10 +33730,10 @@
         <v>976</v>
       </c>
       <c r="G400" t="s" s="7">
+        <v>2178</v>
+      </c>
+      <c r="H400" t="s" s="7">
         <v>2179</v>
-      </c>
-      <c r="H400" t="s" s="7">
-        <v>2180</v>
       </c>
       <c r="I400" t="s" s="7">
         <v>204</v>
@@ -33750,7 +33747,7 @@
       <c r="N400" s="9"/>
       <c r="O400" s="9"/>
       <c r="P400" t="s" s="7">
-        <v>2181</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="401" ht="15.35" customHeight="1">
@@ -33773,10 +33770,10 @@
         <v>980</v>
       </c>
       <c r="G401" t="s" s="7">
+        <v>2181</v>
+      </c>
+      <c r="H401" t="s" s="7">
         <v>2182</v>
-      </c>
-      <c r="H401" t="s" s="7">
-        <v>2183</v>
       </c>
       <c r="I401" t="s" s="7">
         <v>254</v>
@@ -33790,7 +33787,7 @@
       <c r="N401" s="9"/>
       <c r="O401" s="9"/>
       <c r="P401" t="s" s="7">
-        <v>2184</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="402" ht="15.35" customHeight="1">
@@ -33813,10 +33810,10 @@
         <v>984</v>
       </c>
       <c r="G402" t="s" s="7">
+        <v>2184</v>
+      </c>
+      <c r="H402" t="s" s="7">
         <v>2185</v>
-      </c>
-      <c r="H402" t="s" s="7">
-        <v>2186</v>
       </c>
       <c r="I402" t="s" s="7">
         <v>204</v>
@@ -33830,7 +33827,7 @@
       <c r="N402" s="9"/>
       <c r="O402" s="9"/>
       <c r="P402" t="s" s="7">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="403" ht="15.35" customHeight="1">
@@ -33853,7 +33850,7 @@
         <v>988</v>
       </c>
       <c r="G403" t="s" s="7">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="H403" t="s" s="7">
         <v>678</v>
@@ -33870,7 +33867,7 @@
       <c r="N403" s="9"/>
       <c r="O403" s="9"/>
       <c r="P403" t="s" s="7">
-        <v>2189</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="404" ht="15.35" customHeight="1">
@@ -33893,10 +33890,10 @@
         <v>992</v>
       </c>
       <c r="G404" t="s" s="7">
+        <v>2189</v>
+      </c>
+      <c r="H404" t="s" s="7">
         <v>2190</v>
-      </c>
-      <c r="H404" t="s" s="7">
-        <v>2191</v>
       </c>
       <c r="I404" t="s" s="7">
         <v>254</v>
@@ -33910,7 +33907,7 @@
       <c r="N404" s="9"/>
       <c r="O404" s="9"/>
       <c r="P404" t="s" s="7">
-        <v>2192</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="405" ht="15.35" customHeight="1">
@@ -33933,10 +33930,10 @@
         <v>996</v>
       </c>
       <c r="G405" t="s" s="7">
+        <v>2192</v>
+      </c>
+      <c r="H405" t="s" s="7">
         <v>2193</v>
-      </c>
-      <c r="H405" t="s" s="7">
-        <v>2194</v>
       </c>
       <c r="I405" t="s" s="7">
         <v>26</v>
@@ -33950,7 +33947,7 @@
       <c r="N405" s="9"/>
       <c r="O405" s="9"/>
       <c r="P405" t="s" s="7">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="406" ht="15.35" customHeight="1">
@@ -33973,10 +33970,10 @@
         <v>1044</v>
       </c>
       <c r="G406" t="s" s="7">
+        <v>2195</v>
+      </c>
+      <c r="H406" t="s" s="7">
         <v>2196</v>
-      </c>
-      <c r="H406" t="s" s="7">
-        <v>2197</v>
       </c>
       <c r="I406" t="s" s="7">
         <v>254</v>
@@ -33990,7 +33987,7 @@
       <c r="N406" s="9"/>
       <c r="O406" s="9"/>
       <c r="P406" t="s" s="7">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="407" ht="15.35" customHeight="1">
@@ -34013,10 +34010,10 @@
         <v>1048</v>
       </c>
       <c r="G407" t="s" s="7">
+        <v>2198</v>
+      </c>
+      <c r="H407" t="s" s="7">
         <v>2199</v>
-      </c>
-      <c r="H407" t="s" s="7">
-        <v>2200</v>
       </c>
       <c r="I407" t="s" s="7">
         <v>254</v>
@@ -34030,7 +34027,7 @@
       <c r="N407" s="9"/>
       <c r="O407" s="9"/>
       <c r="P407" t="s" s="7">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="408" ht="15.35" customHeight="1">
@@ -34053,10 +34050,10 @@
         <v>1052</v>
       </c>
       <c r="G408" t="s" s="7">
+        <v>2201</v>
+      </c>
+      <c r="H408" t="s" s="7">
         <v>2202</v>
-      </c>
-      <c r="H408" t="s" s="7">
-        <v>2203</v>
       </c>
       <c r="I408" t="s" s="7">
         <v>254</v>
@@ -34070,7 +34067,7 @@
       <c r="N408" s="9"/>
       <c r="O408" s="9"/>
       <c r="P408" t="s" s="7">
-        <v>2204</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="409" ht="15.35" customHeight="1">
@@ -34093,10 +34090,10 @@
         <v>1056</v>
       </c>
       <c r="G409" t="s" s="7">
+        <v>2204</v>
+      </c>
+      <c r="H409" t="s" s="7">
         <v>2205</v>
-      </c>
-      <c r="H409" t="s" s="7">
-        <v>2206</v>
       </c>
       <c r="I409" t="s" s="7">
         <v>626</v>
@@ -34110,7 +34107,7 @@
       <c r="N409" s="9"/>
       <c r="O409" s="9"/>
       <c r="P409" t="s" s="7">
-        <v>2207</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="410" ht="15.35" customHeight="1">
@@ -34133,10 +34130,10 @@
         <v>1060</v>
       </c>
       <c r="G410" t="s" s="7">
+        <v>2207</v>
+      </c>
+      <c r="H410" t="s" s="7">
         <v>2208</v>
-      </c>
-      <c r="H410" t="s" s="7">
-        <v>2209</v>
       </c>
       <c r="I410" t="s" s="7">
         <v>254</v>
@@ -34150,7 +34147,7 @@
       <c r="N410" s="9"/>
       <c r="O410" s="9"/>
       <c r="P410" t="s" s="7">
-        <v>2210</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="411" ht="15.35" customHeight="1">
@@ -34173,10 +34170,10 @@
         <v>1064</v>
       </c>
       <c r="G411" t="s" s="7">
+        <v>2210</v>
+      </c>
+      <c r="H411" t="s" s="7">
         <v>2211</v>
-      </c>
-      <c r="H411" t="s" s="7">
-        <v>2212</v>
       </c>
       <c r="I411" t="s" s="7">
         <v>254</v>
@@ -34190,7 +34187,7 @@
       <c r="N411" s="9"/>
       <c r="O411" s="9"/>
       <c r="P411" t="s" s="7">
-        <v>2213</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="412" ht="15.35" customHeight="1">
@@ -34213,10 +34210,10 @@
         <v>1068</v>
       </c>
       <c r="G412" t="s" s="7">
+        <v>2213</v>
+      </c>
+      <c r="H412" t="s" s="7">
         <v>2214</v>
-      </c>
-      <c r="H412" t="s" s="7">
-        <v>2215</v>
       </c>
       <c r="I412" t="s" s="7">
         <v>254</v>
@@ -34230,7 +34227,7 @@
       <c r="N412" s="9"/>
       <c r="O412" s="9"/>
       <c r="P412" t="s" s="7">
-        <v>2216</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="413" ht="15.35" customHeight="1">
@@ -34253,10 +34250,10 @@
         <v>1072</v>
       </c>
       <c r="G413" t="s" s="7">
+        <v>2216</v>
+      </c>
+      <c r="H413" t="s" s="7">
         <v>2217</v>
-      </c>
-      <c r="H413" t="s" s="7">
-        <v>2218</v>
       </c>
       <c r="I413" t="s" s="7">
         <v>204</v>
@@ -34270,7 +34267,7 @@
       <c r="N413" s="9"/>
       <c r="O413" s="9"/>
       <c r="P413" t="s" s="7">
-        <v>2219</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="414" ht="15.35" customHeight="1">
@@ -34293,10 +34290,10 @@
         <v>1076</v>
       </c>
       <c r="G414" t="s" s="7">
+        <v>2219</v>
+      </c>
+      <c r="H414" t="s" s="7">
         <v>2220</v>
-      </c>
-      <c r="H414" t="s" s="7">
-        <v>2221</v>
       </c>
       <c r="I414" t="s" s="7">
         <v>254</v>
@@ -34310,7 +34307,7 @@
       <c r="N414" s="9"/>
       <c r="O414" s="9"/>
       <c r="P414" t="s" s="7">
-        <v>2222</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="415" ht="15.35" customHeight="1">
@@ -34333,10 +34330,10 @@
         <v>1080</v>
       </c>
       <c r="G415" t="s" s="7">
+        <v>2222</v>
+      </c>
+      <c r="H415" t="s" s="7">
         <v>2223</v>
-      </c>
-      <c r="H415" t="s" s="7">
-        <v>2224</v>
       </c>
       <c r="I415" t="s" s="7">
         <v>254</v>
@@ -34350,7 +34347,7 @@
       <c r="N415" s="9"/>
       <c r="O415" s="9"/>
       <c r="P415" t="s" s="7">
-        <v>2225</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="416" ht="15.35" customHeight="1">
@@ -34373,10 +34370,10 @@
         <v>1084</v>
       </c>
       <c r="G416" t="s" s="7">
+        <v>2225</v>
+      </c>
+      <c r="H416" t="s" s="7">
         <v>2226</v>
-      </c>
-      <c r="H416" t="s" s="7">
-        <v>2227</v>
       </c>
       <c r="I416" t="s" s="7">
         <v>254</v>
@@ -34390,7 +34387,7 @@
       <c r="N416" s="9"/>
       <c r="O416" s="9"/>
       <c r="P416" t="s" s="7">
-        <v>2228</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="417" ht="15.35" customHeight="1">
@@ -34413,10 +34410,10 @@
         <v>1088</v>
       </c>
       <c r="G417" t="s" s="7">
+        <v>2228</v>
+      </c>
+      <c r="H417" t="s" s="7">
         <v>2229</v>
-      </c>
-      <c r="H417" t="s" s="7">
-        <v>2230</v>
       </c>
       <c r="I417" t="s" s="7">
         <v>254</v>
@@ -34430,7 +34427,7 @@
       <c r="N417" s="9"/>
       <c r="O417" s="9"/>
       <c r="P417" t="s" s="7">
-        <v>2231</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="418" ht="15.35" customHeight="1">
@@ -34453,10 +34450,10 @@
         <v>1092</v>
       </c>
       <c r="G418" t="s" s="7">
+        <v>2231</v>
+      </c>
+      <c r="H418" t="s" s="7">
         <v>2232</v>
-      </c>
-      <c r="H418" t="s" s="7">
-        <v>2233</v>
       </c>
       <c r="I418" t="s" s="7">
         <v>204</v>
@@ -34470,7 +34467,7 @@
       <c r="N418" s="9"/>
       <c r="O418" s="9"/>
       <c r="P418" t="s" s="7">
-        <v>2234</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="419" ht="15.35" customHeight="1">
@@ -34493,10 +34490,10 @@
         <v>1096</v>
       </c>
       <c r="G419" t="s" s="7">
+        <v>2234</v>
+      </c>
+      <c r="H419" t="s" s="7">
         <v>2235</v>
-      </c>
-      <c r="H419" t="s" s="7">
-        <v>2236</v>
       </c>
       <c r="I419" t="s" s="7">
         <v>254</v>
@@ -34510,7 +34507,7 @@
       <c r="N419" s="9"/>
       <c r="O419" s="9"/>
       <c r="P419" t="s" s="7">
-        <v>2237</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="420" ht="15.35" customHeight="1">
@@ -34536,7 +34533,7 @@
         <v>1263</v>
       </c>
       <c r="H420" t="s" s="7">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="I420" t="s" s="7">
         <v>626</v>
@@ -34550,7 +34547,7 @@
       <c r="N420" s="9"/>
       <c r="O420" s="9"/>
       <c r="P420" t="s" s="7">
-        <v>2239</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="421" ht="15.35" customHeight="1">
@@ -34573,10 +34570,10 @@
         <v>1104</v>
       </c>
       <c r="G421" t="s" s="7">
+        <v>2239</v>
+      </c>
+      <c r="H421" t="s" s="7">
         <v>2240</v>
-      </c>
-      <c r="H421" t="s" s="7">
-        <v>2241</v>
       </c>
       <c r="I421" t="s" s="7">
         <v>324</v>
@@ -34590,7 +34587,7 @@
       <c r="N421" s="9"/>
       <c r="O421" s="9"/>
       <c r="P421" t="s" s="7">
-        <v>2242</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="422" ht="15.35" customHeight="1">
@@ -34613,10 +34610,10 @@
         <v>1108</v>
       </c>
       <c r="G422" t="s" s="7">
+        <v>2242</v>
+      </c>
+      <c r="H422" t="s" s="7">
         <v>2243</v>
-      </c>
-      <c r="H422" t="s" s="7">
-        <v>2244</v>
       </c>
       <c r="I422" t="s" s="7">
         <v>32</v>
@@ -34630,7 +34627,7 @@
       <c r="N422" s="9"/>
       <c r="O422" s="9"/>
       <c r="P422" t="s" s="7">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="423" ht="15.35" customHeight="1">
@@ -34653,10 +34650,10 @@
         <v>1112</v>
       </c>
       <c r="G423" t="s" s="7">
+        <v>2245</v>
+      </c>
+      <c r="H423" t="s" s="7">
         <v>2246</v>
-      </c>
-      <c r="H423" t="s" s="7">
-        <v>2247</v>
       </c>
       <c r="I423" t="s" s="7">
         <v>324</v>
@@ -34670,7 +34667,7 @@
       <c r="N423" s="9"/>
       <c r="O423" s="9"/>
       <c r="P423" t="s" s="7">
-        <v>2248</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="424" ht="15.35" customHeight="1">
@@ -34693,10 +34690,10 @@
         <v>1116</v>
       </c>
       <c r="G424" t="s" s="7">
+        <v>2248</v>
+      </c>
+      <c r="H424" t="s" s="7">
         <v>2249</v>
-      </c>
-      <c r="H424" t="s" s="7">
-        <v>2250</v>
       </c>
       <c r="I424" t="s" s="7">
         <v>254</v>
@@ -34710,7 +34707,7 @@
       <c r="N424" s="9"/>
       <c r="O424" s="9"/>
       <c r="P424" t="s" s="7">
-        <v>2251</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="425" ht="15.35" customHeight="1">
@@ -34733,10 +34730,10 @@
         <v>1120</v>
       </c>
       <c r="G425" t="s" s="7">
+        <v>2251</v>
+      </c>
+      <c r="H425" t="s" s="7">
         <v>2252</v>
-      </c>
-      <c r="H425" t="s" s="7">
-        <v>2253</v>
       </c>
       <c r="I425" t="s" s="7">
         <v>254</v>
@@ -34750,7 +34747,7 @@
       <c r="N425" s="9"/>
       <c r="O425" s="9"/>
       <c r="P425" t="s" s="7">
-        <v>2254</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="426" ht="15.35" customHeight="1">
@@ -34773,10 +34770,10 @@
         <v>1125</v>
       </c>
       <c r="G426" t="s" s="7">
+        <v>2254</v>
+      </c>
+      <c r="H426" t="s" s="7">
         <v>2255</v>
-      </c>
-      <c r="H426" t="s" s="7">
-        <v>2256</v>
       </c>
       <c r="I426" t="s" s="7">
         <v>254</v>
@@ -34790,7 +34787,7 @@
       <c r="N426" s="9"/>
       <c r="O426" s="9"/>
       <c r="P426" t="s" s="7">
-        <v>2257</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="427" ht="15.35" customHeight="1">
@@ -34813,10 +34810,10 @@
         <v>1235</v>
       </c>
       <c r="G427" t="s" s="7">
+        <v>2257</v>
+      </c>
+      <c r="H427" t="s" s="7">
         <v>2258</v>
-      </c>
-      <c r="H427" t="s" s="7">
-        <v>2259</v>
       </c>
       <c r="I427" t="s" s="7">
         <v>254</v>
@@ -34830,7 +34827,7 @@
       <c r="N427" s="9"/>
       <c r="O427" s="9"/>
       <c r="P427" t="s" s="7">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="428" ht="15.35" customHeight="1">
@@ -34853,10 +34850,10 @@
         <v>1239</v>
       </c>
       <c r="G428" t="s" s="7">
+        <v>2260</v>
+      </c>
+      <c r="H428" t="s" s="7">
         <v>2261</v>
-      </c>
-      <c r="H428" t="s" s="7">
-        <v>2262</v>
       </c>
       <c r="I428" t="s" s="7">
         <v>254</v>
@@ -34870,7 +34867,7 @@
       <c r="N428" s="9"/>
       <c r="O428" s="9"/>
       <c r="P428" t="s" s="7">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="429" ht="15.35" customHeight="1">
@@ -34893,10 +34890,10 @@
         <v>1243</v>
       </c>
       <c r="G429" t="s" s="7">
+        <v>2263</v>
+      </c>
+      <c r="H429" t="s" s="7">
         <v>2264</v>
-      </c>
-      <c r="H429" t="s" s="7">
-        <v>2265</v>
       </c>
       <c r="I429" t="s" s="7">
         <v>254</v>
@@ -34910,7 +34907,7 @@
       <c r="N429" s="9"/>
       <c r="O429" s="9"/>
       <c r="P429" t="s" s="7">
-        <v>2266</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="430" ht="15.35" customHeight="1">
@@ -34933,10 +34930,10 @@
         <v>1247</v>
       </c>
       <c r="G430" t="s" s="7">
+        <v>2266</v>
+      </c>
+      <c r="H430" t="s" s="7">
         <v>2267</v>
-      </c>
-      <c r="H430" t="s" s="7">
-        <v>2268</v>
       </c>
       <c r="I430" t="s" s="7">
         <v>254</v>
@@ -34950,7 +34947,7 @@
       <c r="N430" s="9"/>
       <c r="O430" s="9"/>
       <c r="P430" t="s" s="7">
-        <v>2269</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="431" ht="15.35" customHeight="1">
@@ -34973,10 +34970,10 @@
         <v>1251</v>
       </c>
       <c r="G431" t="s" s="7">
+        <v>2269</v>
+      </c>
+      <c r="H431" t="s" s="7">
         <v>2270</v>
-      </c>
-      <c r="H431" t="s" s="7">
-        <v>2271</v>
       </c>
       <c r="I431" t="s" s="7">
         <v>617</v>
@@ -34990,7 +34987,7 @@
       <c r="N431" s="9"/>
       <c r="O431" s="9"/>
       <c r="P431" t="s" s="7">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="432" ht="15.35" customHeight="1">
@@ -35013,10 +35010,10 @@
         <v>1255</v>
       </c>
       <c r="G432" t="s" s="7">
+        <v>2272</v>
+      </c>
+      <c r="H432" t="s" s="7">
         <v>2273</v>
-      </c>
-      <c r="H432" t="s" s="7">
-        <v>2274</v>
       </c>
       <c r="I432" t="s" s="7">
         <v>204</v>
@@ -35030,7 +35027,7 @@
       <c r="N432" s="9"/>
       <c r="O432" s="9"/>
       <c r="P432" t="s" s="7">
-        <v>2275</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="433" ht="15.35" customHeight="1">
@@ -35053,10 +35050,10 @@
         <v>1259</v>
       </c>
       <c r="G433" t="s" s="7">
+        <v>2275</v>
+      </c>
+      <c r="H433" t="s" s="7">
         <v>2276</v>
-      </c>
-      <c r="H433" t="s" s="7">
-        <v>2277</v>
       </c>
       <c r="I433" t="s" s="7">
         <v>254</v>
@@ -35070,7 +35067,7 @@
       <c r="N433" s="9"/>
       <c r="O433" s="9"/>
       <c r="P433" t="s" s="7">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="434" ht="15.35" customHeight="1">
@@ -35093,10 +35090,10 @@
         <v>1262</v>
       </c>
       <c r="G434" t="s" s="7">
+        <v>2278</v>
+      </c>
+      <c r="H434" t="s" s="7">
         <v>2279</v>
-      </c>
-      <c r="H434" t="s" s="7">
-        <v>2280</v>
       </c>
       <c r="I434" t="s" s="7">
         <v>254</v>
@@ -35110,7 +35107,7 @@
       <c r="N434" s="9"/>
       <c r="O434" s="9"/>
       <c r="P434" t="s" s="7">
-        <v>2281</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="435" ht="15.35" customHeight="1">
@@ -35133,10 +35130,10 @@
         <v>1266</v>
       </c>
       <c r="G435" t="s" s="7">
+        <v>2281</v>
+      </c>
+      <c r="H435" t="s" s="7">
         <v>2282</v>
-      </c>
-      <c r="H435" t="s" s="7">
-        <v>2283</v>
       </c>
       <c r="I435" t="s" s="7">
         <v>204</v>
@@ -35150,7 +35147,7 @@
       <c r="N435" s="9"/>
       <c r="O435" s="9"/>
       <c r="P435" t="s" s="7">
-        <v>2284</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="436" ht="15.35" customHeight="1">
@@ -35173,7 +35170,7 @@
         <v>1617</v>
       </c>
       <c r="G436" t="s" s="7">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="H436" t="s" s="7">
         <v>682</v>
@@ -35190,7 +35187,7 @@
       <c r="N436" s="9"/>
       <c r="O436" s="9"/>
       <c r="P436" t="s" s="7">
-        <v>2286</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="437" ht="15.35" customHeight="1">
@@ -35213,10 +35210,10 @@
         <v>1621</v>
       </c>
       <c r="G437" t="s" s="7">
+        <v>2286</v>
+      </c>
+      <c r="H437" t="s" s="7">
         <v>2287</v>
-      </c>
-      <c r="H437" t="s" s="7">
-        <v>2288</v>
       </c>
       <c r="I437" t="s" s="7">
         <v>254</v>
@@ -35230,7 +35227,7 @@
       <c r="N437" s="9"/>
       <c r="O437" s="9"/>
       <c r="P437" t="s" s="7">
-        <v>2289</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="438" ht="15.35" customHeight="1">
@@ -35253,10 +35250,10 @@
         <v>1625</v>
       </c>
       <c r="G438" t="s" s="7">
+        <v>2289</v>
+      </c>
+      <c r="H438" t="s" s="7">
         <v>2290</v>
-      </c>
-      <c r="H438" t="s" s="7">
-        <v>2291</v>
       </c>
       <c r="I438" t="s" s="7">
         <v>204</v>
@@ -35270,7 +35267,7 @@
       <c r="N438" s="9"/>
       <c r="O438" s="9"/>
       <c r="P438" t="s" s="7">
-        <v>2292</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="439" ht="15.35" customHeight="1">
@@ -35293,10 +35290,10 @@
         <v>1629</v>
       </c>
       <c r="G439" t="s" s="7">
+        <v>2292</v>
+      </c>
+      <c r="H439" t="s" s="7">
         <v>2293</v>
-      </c>
-      <c r="H439" t="s" s="7">
-        <v>2294</v>
       </c>
       <c r="I439" t="s" s="7">
         <v>254</v>
@@ -35310,7 +35307,7 @@
       <c r="N439" s="9"/>
       <c r="O439" s="9"/>
       <c r="P439" t="s" s="7">
-        <v>2295</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="440" ht="15.35" customHeight="1">
@@ -35333,10 +35330,10 @@
         <v>1633</v>
       </c>
       <c r="G440" t="s" s="7">
+        <v>2295</v>
+      </c>
+      <c r="H440" t="s" s="7">
         <v>2296</v>
-      </c>
-      <c r="H440" t="s" s="7">
-        <v>2297</v>
       </c>
       <c r="I440" t="s" s="7">
         <v>254</v>
@@ -35350,7 +35347,7 @@
       <c r="N440" s="9"/>
       <c r="O440" s="9"/>
       <c r="P440" t="s" s="7">
-        <v>2298</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="441" ht="15.35" customHeight="1">
@@ -35373,10 +35370,10 @@
         <v>1637</v>
       </c>
       <c r="G441" t="s" s="7">
+        <v>2298</v>
+      </c>
+      <c r="H441" t="s" s="7">
         <v>2299</v>
-      </c>
-      <c r="H441" t="s" s="7">
-        <v>2300</v>
       </c>
       <c r="I441" t="s" s="7">
         <v>87</v>
@@ -35390,7 +35387,7 @@
       <c r="N441" s="9"/>
       <c r="O441" s="9"/>
       <c r="P441" t="s" s="7">
-        <v>2301</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="442" ht="15.35" customHeight="1">
@@ -35413,10 +35410,10 @@
         <v>1641</v>
       </c>
       <c r="G442" t="s" s="7">
+        <v>2301</v>
+      </c>
+      <c r="H442" t="s" s="7">
         <v>2302</v>
-      </c>
-      <c r="H442" t="s" s="7">
-        <v>2303</v>
       </c>
       <c r="I442" t="s" s="7">
         <v>204</v>
@@ -35430,7 +35427,7 @@
       <c r="N442" s="9"/>
       <c r="O442" s="9"/>
       <c r="P442" t="s" s="7">
-        <v>2304</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="443" ht="15.35" customHeight="1">
@@ -35453,7 +35450,7 @@
         <v>1645</v>
       </c>
       <c r="G443" t="s" s="7">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="H443" t="s" s="7">
         <v>638</v>
@@ -35470,7 +35467,7 @@
       <c r="N443" s="9"/>
       <c r="O443" s="9"/>
       <c r="P443" t="s" s="7">
-        <v>2306</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="444" ht="15.35" customHeight="1">
@@ -35493,10 +35490,10 @@
         <v>1649</v>
       </c>
       <c r="G444" t="s" s="7">
+        <v>2306</v>
+      </c>
+      <c r="H444" t="s" s="7">
         <v>2307</v>
-      </c>
-      <c r="H444" t="s" s="7">
-        <v>2308</v>
       </c>
       <c r="I444" t="s" s="7">
         <v>254</v>
@@ -35510,7 +35507,7 @@
       <c r="N444" s="9"/>
       <c r="O444" s="9"/>
       <c r="P444" t="s" s="7">
-        <v>2309</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="445" ht="15.35" customHeight="1">
@@ -35533,10 +35530,10 @@
         <v>1653</v>
       </c>
       <c r="G445" t="s" s="7">
+        <v>2309</v>
+      </c>
+      <c r="H445" t="s" s="7">
         <v>2310</v>
-      </c>
-      <c r="H445" t="s" s="7">
-        <v>2311</v>
       </c>
       <c r="I445" t="s" s="7">
         <v>626</v>
@@ -35550,7 +35547,7 @@
       <c r="N445" s="9"/>
       <c r="O445" s="9"/>
       <c r="P445" t="s" s="7">
-        <v>2312</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="446" ht="15.35" customHeight="1">
@@ -35573,10 +35570,10 @@
         <v>1657</v>
       </c>
       <c r="G446" t="s" s="7">
+        <v>2312</v>
+      </c>
+      <c r="H446" t="s" s="7">
         <v>2313</v>
-      </c>
-      <c r="H446" t="s" s="7">
-        <v>2314</v>
       </c>
       <c r="I446" t="s" s="7">
         <v>254</v>
@@ -35590,7 +35587,7 @@
       <c r="N446" s="9"/>
       <c r="O446" s="9"/>
       <c r="P446" t="s" s="7">
-        <v>2315</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="447" ht="15.35" customHeight="1">
@@ -35613,13 +35610,13 @@
         <v>940</v>
       </c>
       <c r="G447" t="s" s="7">
+        <v>2315</v>
+      </c>
+      <c r="H447" t="s" s="7">
         <v>2316</v>
       </c>
-      <c r="H447" t="s" s="7">
+      <c r="I447" t="s" s="7">
         <v>2317</v>
-      </c>
-      <c r="I447" t="s" s="7">
-        <v>2318</v>
       </c>
       <c r="J447" t="s" s="7">
         <v>27</v>
@@ -35630,7 +35627,7 @@
       <c r="N447" s="9"/>
       <c r="O447" s="9"/>
       <c r="P447" t="s" s="7">
-        <v>2319</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="448" ht="15.35" customHeight="1">
@@ -35653,10 +35650,10 @@
         <v>944</v>
       </c>
       <c r="G448" t="s" s="7">
+        <v>2319</v>
+      </c>
+      <c r="H448" t="s" s="7">
         <v>2320</v>
-      </c>
-      <c r="H448" t="s" s="7">
-        <v>2321</v>
       </c>
       <c r="I448" t="s" s="7">
         <v>254</v>
@@ -35670,7 +35667,7 @@
       <c r="N448" s="9"/>
       <c r="O448" s="9"/>
       <c r="P448" t="s" s="7">
-        <v>2322</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="449" ht="15.35" customHeight="1">
@@ -35693,13 +35690,13 @@
         <v>948</v>
       </c>
       <c r="G449" t="s" s="7">
+        <v>2322</v>
+      </c>
+      <c r="H449" t="s" s="7">
         <v>2323</v>
       </c>
-      <c r="H449" t="s" s="7">
-        <v>2324</v>
-      </c>
       <c r="I449" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J449" t="s" s="7">
         <v>27</v>
@@ -35710,7 +35707,7 @@
       <c r="N449" s="9"/>
       <c r="O449" s="9"/>
       <c r="P449" t="s" s="7">
-        <v>2325</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="450" ht="15.35" customHeight="1">
@@ -35733,13 +35730,13 @@
         <v>952</v>
       </c>
       <c r="G450" t="s" s="7">
+        <v>2325</v>
+      </c>
+      <c r="H450" t="s" s="7">
         <v>2326</v>
       </c>
-      <c r="H450" t="s" s="7">
-        <v>2327</v>
-      </c>
       <c r="I450" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J450" t="s" s="7">
         <v>27</v>
@@ -35750,7 +35747,7 @@
       <c r="N450" s="9"/>
       <c r="O450" s="9"/>
       <c r="P450" t="s" s="7">
-        <v>2328</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="451" ht="15.35" customHeight="1">
@@ -35773,10 +35770,10 @@
         <v>956</v>
       </c>
       <c r="G451" t="s" s="7">
+        <v>2328</v>
+      </c>
+      <c r="H451" t="s" s="7">
         <v>2329</v>
-      </c>
-      <c r="H451" t="s" s="7">
-        <v>2330</v>
       </c>
       <c r="I451" t="s" s="7">
         <v>803</v>
@@ -35790,7 +35787,7 @@
       <c r="N451" s="9"/>
       <c r="O451" s="9"/>
       <c r="P451" t="s" s="7">
-        <v>2331</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="452" ht="15.35" customHeight="1">
@@ -35813,10 +35810,10 @@
         <v>960</v>
       </c>
       <c r="G452" t="s" s="7">
+        <v>2331</v>
+      </c>
+      <c r="H452" t="s" s="7">
         <v>2332</v>
-      </c>
-      <c r="H452" t="s" s="7">
-        <v>2333</v>
       </c>
       <c r="I452" t="s" s="7">
         <v>704</v>
@@ -35830,7 +35827,7 @@
       <c r="N452" s="9"/>
       <c r="O452" s="9"/>
       <c r="P452" t="s" s="7">
-        <v>2334</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="453" ht="15.35" customHeight="1">
@@ -35853,10 +35850,10 @@
         <v>964</v>
       </c>
       <c r="G453" t="s" s="7">
+        <v>2334</v>
+      </c>
+      <c r="H453" t="s" s="7">
         <v>2335</v>
-      </c>
-      <c r="H453" t="s" s="7">
-        <v>2336</v>
       </c>
       <c r="I453" t="s" s="7">
         <v>803</v>
@@ -35870,7 +35867,7 @@
       <c r="N453" s="9"/>
       <c r="O453" s="9"/>
       <c r="P453" t="s" s="7">
-        <v>2337</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="454" ht="15.35" customHeight="1">
@@ -35893,10 +35890,10 @@
         <v>968</v>
       </c>
       <c r="G454" t="s" s="7">
+        <v>2337</v>
+      </c>
+      <c r="H454" t="s" s="7">
         <v>2338</v>
-      </c>
-      <c r="H454" t="s" s="7">
-        <v>2339</v>
       </c>
       <c r="I454" t="s" s="7">
         <v>704</v>
@@ -35910,7 +35907,7 @@
       <c r="N454" s="9"/>
       <c r="O454" s="9"/>
       <c r="P454" t="s" s="7">
-        <v>2340</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="455" ht="15.35" customHeight="1">
@@ -35933,13 +35930,13 @@
         <v>972</v>
       </c>
       <c r="G455" t="s" s="7">
+        <v>2340</v>
+      </c>
+      <c r="H455" t="s" s="7">
         <v>2341</v>
       </c>
-      <c r="H455" t="s" s="7">
-        <v>2342</v>
-      </c>
       <c r="I455" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J455" t="s" s="7">
         <v>27</v>
@@ -35950,7 +35947,7 @@
       <c r="N455" s="9"/>
       <c r="O455" s="9"/>
       <c r="P455" t="s" s="7">
-        <v>2343</v>
+        <v>2342</v>
       </c>
     </row>
     <row r="456" ht="15.35" customHeight="1">
@@ -35973,10 +35970,10 @@
         <v>976</v>
       </c>
       <c r="G456" t="s" s="7">
+        <v>2343</v>
+      </c>
+      <c r="H456" t="s" s="7">
         <v>2344</v>
-      </c>
-      <c r="H456" t="s" s="7">
-        <v>2345</v>
       </c>
       <c r="I456" t="s" s="7">
         <v>714</v>
@@ -35990,7 +35987,7 @@
       <c r="N456" s="9"/>
       <c r="O456" s="9"/>
       <c r="P456" t="s" s="7">
-        <v>2346</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="457" ht="15.35" customHeight="1">
@@ -36013,7 +36010,7 @@
         <v>980</v>
       </c>
       <c r="G457" t="s" s="7">
-        <v>2347</v>
+        <v>2346</v>
       </c>
       <c r="H457" t="s" s="7">
         <v>735</v>
@@ -36030,7 +36027,7 @@
       <c r="N457" s="9"/>
       <c r="O457" s="9"/>
       <c r="P457" t="s" s="7">
-        <v>2348</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="458" ht="15.35" customHeight="1">
@@ -36053,13 +36050,13 @@
         <v>984</v>
       </c>
       <c r="G458" t="s" s="7">
+        <v>2348</v>
+      </c>
+      <c r="H458" t="s" s="7">
         <v>2349</v>
       </c>
-      <c r="H458" t="s" s="7">
-        <v>2350</v>
-      </c>
       <c r="I458" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J458" t="s" s="7">
         <v>42</v>
@@ -36070,7 +36067,7 @@
       <c r="N458" s="9"/>
       <c r="O458" s="9"/>
       <c r="P458" t="s" s="7">
-        <v>2351</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="459" ht="15.35" customHeight="1">
@@ -36093,13 +36090,13 @@
         <v>988</v>
       </c>
       <c r="G459" t="s" s="7">
+        <v>2351</v>
+      </c>
+      <c r="H459" t="s" s="7">
         <v>2352</v>
       </c>
-      <c r="H459" t="s" s="7">
-        <v>2353</v>
-      </c>
       <c r="I459" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J459" t="s" s="7">
         <v>27</v>
@@ -36110,7 +36107,7 @@
       <c r="N459" s="9"/>
       <c r="O459" s="9"/>
       <c r="P459" t="s" s="7">
-        <v>2354</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="460" ht="15.35" customHeight="1">
@@ -36133,7 +36130,7 @@
         <v>992</v>
       </c>
       <c r="G460" t="s" s="7">
-        <v>2355</v>
+        <v>2354</v>
       </c>
       <c r="H460" t="s" s="7">
         <v>718</v>
@@ -36150,7 +36147,7 @@
       <c r="N460" s="9"/>
       <c r="O460" s="9"/>
       <c r="P460" t="s" s="7">
-        <v>2356</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="461" ht="15.35" customHeight="1">
@@ -36173,10 +36170,10 @@
         <v>996</v>
       </c>
       <c r="G461" t="s" s="7">
+        <v>2356</v>
+      </c>
+      <c r="H461" t="s" s="7">
         <v>2357</v>
-      </c>
-      <c r="H461" t="s" s="7">
-        <v>2358</v>
       </c>
       <c r="I461" t="s" s="7">
         <v>803</v>
@@ -36190,7 +36187,7 @@
       <c r="N461" s="9"/>
       <c r="O461" s="9"/>
       <c r="P461" t="s" s="7">
-        <v>2359</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="462" ht="15.35" customHeight="1">
@@ -36213,10 +36210,10 @@
         <v>1044</v>
       </c>
       <c r="G462" t="s" s="7">
+        <v>2359</v>
+      </c>
+      <c r="H462" t="s" s="7">
         <v>2360</v>
-      </c>
-      <c r="H462" t="s" s="7">
-        <v>2361</v>
       </c>
       <c r="I462" t="s" s="7">
         <v>26</v>
@@ -36230,7 +36227,7 @@
       <c r="N462" s="9"/>
       <c r="O462" s="9"/>
       <c r="P462" t="s" s="7">
-        <v>2362</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="463" ht="15.35" customHeight="1">
@@ -36253,10 +36250,10 @@
         <v>1048</v>
       </c>
       <c r="G463" t="s" s="7">
+        <v>2362</v>
+      </c>
+      <c r="H463" t="s" s="7">
         <v>2363</v>
-      </c>
-      <c r="H463" t="s" s="7">
-        <v>2364</v>
       </c>
       <c r="I463" t="s" s="7">
         <v>714</v>
@@ -36270,7 +36267,7 @@
       <c r="N463" s="9"/>
       <c r="O463" s="9"/>
       <c r="P463" t="s" s="7">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="464" ht="15.35" customHeight="1">
@@ -36293,10 +36290,10 @@
         <v>1052</v>
       </c>
       <c r="G464" t="s" s="7">
+        <v>2365</v>
+      </c>
+      <c r="H464" t="s" s="7">
         <v>2366</v>
-      </c>
-      <c r="H464" t="s" s="7">
-        <v>2367</v>
       </c>
       <c r="I464" t="s" s="7">
         <v>714</v>
@@ -36310,7 +36307,7 @@
       <c r="N464" s="9"/>
       <c r="O464" s="9"/>
       <c r="P464" t="s" s="7">
-        <v>2368</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="465" ht="15.35" customHeight="1">
@@ -36333,10 +36330,10 @@
         <v>1056</v>
       </c>
       <c r="G465" t="s" s="7">
+        <v>2368</v>
+      </c>
+      <c r="H465" t="s" s="7">
         <v>2369</v>
-      </c>
-      <c r="H465" t="s" s="7">
-        <v>2370</v>
       </c>
       <c r="I465" t="s" s="7">
         <v>714</v>
@@ -36350,7 +36347,7 @@
       <c r="N465" s="9"/>
       <c r="O465" s="9"/>
       <c r="P465" t="s" s="7">
-        <v>2371</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="466" ht="15.35" customHeight="1">
@@ -36373,10 +36370,10 @@
         <v>1060</v>
       </c>
       <c r="G466" t="s" s="7">
+        <v>2371</v>
+      </c>
+      <c r="H466" t="s" s="7">
         <v>2372</v>
-      </c>
-      <c r="H466" t="s" s="7">
-        <v>2373</v>
       </c>
       <c r="I466" t="s" s="7">
         <v>714</v>
@@ -36390,7 +36387,7 @@
       <c r="N466" s="9"/>
       <c r="O466" s="9"/>
       <c r="P466" t="s" s="7">
-        <v>2374</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="467" ht="15.35" customHeight="1">
@@ -36413,10 +36410,10 @@
         <v>1064</v>
       </c>
       <c r="G467" t="s" s="7">
+        <v>2374</v>
+      </c>
+      <c r="H467" t="s" s="7">
         <v>2375</v>
-      </c>
-      <c r="H467" t="s" s="7">
-        <v>2376</v>
       </c>
       <c r="I467" t="s" s="7">
         <v>714</v>
@@ -36430,7 +36427,7 @@
       <c r="N467" s="9"/>
       <c r="O467" s="9"/>
       <c r="P467" t="s" s="7">
-        <v>2377</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="468" ht="15.35" customHeight="1">
@@ -36453,10 +36450,10 @@
         <v>1068</v>
       </c>
       <c r="G468" t="s" s="7">
+        <v>2377</v>
+      </c>
+      <c r="H468" t="s" s="7">
         <v>2378</v>
-      </c>
-      <c r="H468" t="s" s="7">
-        <v>2379</v>
       </c>
       <c r="I468" t="s" s="7">
         <v>714</v>
@@ -36470,7 +36467,7 @@
       <c r="N468" s="9"/>
       <c r="O468" s="9"/>
       <c r="P468" t="s" s="7">
-        <v>2380</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="469" ht="15.35" customHeight="1">
@@ -36493,10 +36490,10 @@
         <v>1072</v>
       </c>
       <c r="G469" t="s" s="7">
+        <v>2380</v>
+      </c>
+      <c r="H469" t="s" s="7">
         <v>2381</v>
-      </c>
-      <c r="H469" t="s" s="7">
-        <v>2382</v>
       </c>
       <c r="I469" t="s" s="7">
         <v>704</v>
@@ -36510,7 +36507,7 @@
       <c r="N469" s="9"/>
       <c r="O469" s="9"/>
       <c r="P469" t="s" s="7">
-        <v>2383</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="470" ht="15.35" customHeight="1">
@@ -36533,10 +36530,10 @@
         <v>1076</v>
       </c>
       <c r="G470" t="s" s="7">
+        <v>2383</v>
+      </c>
+      <c r="H470" t="s" s="7">
         <v>2384</v>
-      </c>
-      <c r="H470" t="s" s="7">
-        <v>2385</v>
       </c>
       <c r="I470" t="s" s="7">
         <v>714</v>
@@ -36550,7 +36547,7 @@
       <c r="N470" s="9"/>
       <c r="O470" s="9"/>
       <c r="P470" t="s" s="7">
-        <v>2386</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="471" ht="15.35" customHeight="1">
@@ -36573,10 +36570,10 @@
         <v>1080</v>
       </c>
       <c r="G471" t="s" s="7">
+        <v>2386</v>
+      </c>
+      <c r="H471" t="s" s="7">
         <v>2387</v>
-      </c>
-      <c r="H471" t="s" s="7">
-        <v>2388</v>
       </c>
       <c r="I471" t="s" s="7">
         <v>714</v>
@@ -36590,7 +36587,7 @@
       <c r="N471" s="9"/>
       <c r="O471" s="9"/>
       <c r="P471" t="s" s="7">
-        <v>2389</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="472" ht="15.35" customHeight="1">
@@ -36613,10 +36610,10 @@
         <v>1084</v>
       </c>
       <c r="G472" t="s" s="7">
+        <v>2389</v>
+      </c>
+      <c r="H472" t="s" s="7">
         <v>2390</v>
-      </c>
-      <c r="H472" t="s" s="7">
-        <v>2391</v>
       </c>
       <c r="I472" t="s" s="7">
         <v>719</v>
@@ -36630,7 +36627,7 @@
       <c r="N472" s="9"/>
       <c r="O472" s="9"/>
       <c r="P472" t="s" s="7">
-        <v>2392</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="473" ht="15.35" customHeight="1">
@@ -36653,10 +36650,10 @@
         <v>1088</v>
       </c>
       <c r="G473" t="s" s="7">
+        <v>2392</v>
+      </c>
+      <c r="H473" t="s" s="7">
         <v>2393</v>
-      </c>
-      <c r="H473" t="s" s="7">
-        <v>2394</v>
       </c>
       <c r="I473" t="s" s="7">
         <v>803</v>
@@ -36670,7 +36667,7 @@
       <c r="N473" s="9"/>
       <c r="O473" s="9"/>
       <c r="P473" t="s" s="7">
-        <v>2395</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="474" ht="15.35" customHeight="1">
@@ -36693,13 +36690,13 @@
         <v>1092</v>
       </c>
       <c r="G474" t="s" s="7">
+        <v>2395</v>
+      </c>
+      <c r="H474" t="s" s="7">
         <v>2396</v>
       </c>
-      <c r="H474" t="s" s="7">
-        <v>2397</v>
-      </c>
       <c r="I474" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J474" t="s" s="7">
         <v>27</v>
@@ -36710,7 +36707,7 @@
       <c r="N474" s="9"/>
       <c r="O474" s="9"/>
       <c r="P474" t="s" s="7">
-        <v>2398</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="475" ht="15.35" customHeight="1">
@@ -36733,13 +36730,13 @@
         <v>1096</v>
       </c>
       <c r="G475" t="s" s="7">
+        <v>2398</v>
+      </c>
+      <c r="H475" t="s" s="7">
         <v>2399</v>
       </c>
-      <c r="H475" t="s" s="7">
-        <v>2400</v>
-      </c>
       <c r="I475" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J475" t="s" s="7">
         <v>27</v>
@@ -36750,7 +36747,7 @@
       <c r="N475" s="9"/>
       <c r="O475" s="9"/>
       <c r="P475" t="s" s="7">
-        <v>2401</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="476" ht="15.35" customHeight="1">
@@ -36773,10 +36770,10 @@
         <v>1100</v>
       </c>
       <c r="G476" t="s" s="7">
+        <v>2401</v>
+      </c>
+      <c r="H476" t="s" s="7">
         <v>2402</v>
-      </c>
-      <c r="H476" t="s" s="7">
-        <v>2403</v>
       </c>
       <c r="I476" t="s" s="7">
         <v>714</v>
@@ -36790,7 +36787,7 @@
       <c r="N476" s="9"/>
       <c r="O476" s="9"/>
       <c r="P476" t="s" s="7">
-        <v>2404</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="477" ht="15.35" customHeight="1">
@@ -36813,13 +36810,13 @@
         <v>1104</v>
       </c>
       <c r="G477" t="s" s="7">
+        <v>2404</v>
+      </c>
+      <c r="H477" t="s" s="7">
         <v>2405</v>
       </c>
-      <c r="H477" t="s" s="7">
-        <v>2406</v>
-      </c>
       <c r="I477" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J477" t="s" s="7">
         <v>27</v>
@@ -36830,7 +36827,7 @@
       <c r="N477" s="9"/>
       <c r="O477" s="9"/>
       <c r="P477" t="s" s="7">
-        <v>2407</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="478" ht="15.35" customHeight="1">
@@ -36853,13 +36850,13 @@
         <v>1108</v>
       </c>
       <c r="G478" t="s" s="7">
+        <v>2407</v>
+      </c>
+      <c r="H478" t="s" s="7">
         <v>2408</v>
       </c>
-      <c r="H478" t="s" s="7">
-        <v>2409</v>
-      </c>
       <c r="I478" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J478" t="s" s="7">
         <v>27</v>
@@ -36870,7 +36867,7 @@
       <c r="N478" s="9"/>
       <c r="O478" s="9"/>
       <c r="P478" t="s" s="7">
-        <v>2410</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="479" ht="15.35" customHeight="1">
@@ -36893,13 +36890,13 @@
         <v>1112</v>
       </c>
       <c r="G479" t="s" s="7">
+        <v>2410</v>
+      </c>
+      <c r="H479" t="s" s="7">
         <v>2411</v>
       </c>
-      <c r="H479" t="s" s="7">
-        <v>2412</v>
-      </c>
       <c r="I479" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J479" t="s" s="7">
         <v>27</v>
@@ -36910,7 +36907,7 @@
       <c r="N479" s="9"/>
       <c r="O479" s="9"/>
       <c r="P479" t="s" s="7">
-        <v>2413</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="480" ht="15.35" customHeight="1">
@@ -36933,10 +36930,10 @@
         <v>1116</v>
       </c>
       <c r="G480" t="s" s="7">
+        <v>2413</v>
+      </c>
+      <c r="H480" t="s" s="7">
         <v>2414</v>
-      </c>
-      <c r="H480" t="s" s="7">
-        <v>2415</v>
       </c>
       <c r="I480" t="s" s="7">
         <v>803</v>
@@ -36950,7 +36947,7 @@
       <c r="N480" s="9"/>
       <c r="O480" s="9"/>
       <c r="P480" t="s" s="7">
-        <v>2416</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="481" ht="15.35" customHeight="1">
@@ -36973,10 +36970,10 @@
         <v>1120</v>
       </c>
       <c r="G481" t="s" s="7">
+        <v>2416</v>
+      </c>
+      <c r="H481" t="s" s="7">
         <v>2417</v>
-      </c>
-      <c r="H481" t="s" s="7">
-        <v>2418</v>
       </c>
       <c r="I481" t="s" s="7">
         <v>714</v>
@@ -36990,7 +36987,7 @@
       <c r="N481" s="9"/>
       <c r="O481" s="9"/>
       <c r="P481" t="s" s="7">
-        <v>2419</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="482" ht="15.35" customHeight="1">
@@ -37013,10 +37010,10 @@
         <v>1125</v>
       </c>
       <c r="G482" t="s" s="7">
+        <v>2419</v>
+      </c>
+      <c r="H482" t="s" s="7">
         <v>2420</v>
-      </c>
-      <c r="H482" t="s" s="7">
-        <v>2421</v>
       </c>
       <c r="I482" t="s" s="7">
         <v>803</v>
@@ -37030,7 +37027,7 @@
       <c r="N482" s="9"/>
       <c r="O482" s="9"/>
       <c r="P482" t="s" s="7">
-        <v>2422</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="483" ht="15.35" customHeight="1">
@@ -37053,13 +37050,13 @@
         <v>1235</v>
       </c>
       <c r="G483" t="s" s="7">
+        <v>2422</v>
+      </c>
+      <c r="H483" t="s" s="7">
         <v>2423</v>
       </c>
-      <c r="H483" t="s" s="7">
-        <v>2424</v>
-      </c>
       <c r="I483" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J483" t="s" s="7">
         <v>27</v>
@@ -37070,7 +37067,7 @@
       <c r="N483" s="9"/>
       <c r="O483" s="9"/>
       <c r="P483" t="s" s="7">
-        <v>2425</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="484" ht="15.35" customHeight="1">
@@ -37093,10 +37090,10 @@
         <v>1239</v>
       </c>
       <c r="G484" t="s" s="7">
+        <v>2425</v>
+      </c>
+      <c r="H484" t="s" s="7">
         <v>2426</v>
-      </c>
-      <c r="H484" t="s" s="7">
-        <v>2427</v>
       </c>
       <c r="I484" t="s" s="7">
         <v>709</v>
@@ -37110,7 +37107,7 @@
       <c r="N484" s="9"/>
       <c r="O484" s="9"/>
       <c r="P484" t="s" s="7">
-        <v>2428</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="485" ht="15.35" customHeight="1">
@@ -37133,7 +37130,7 @@
         <v>1243</v>
       </c>
       <c r="G485" t="s" s="7">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="H485" t="s" s="7">
         <v>760</v>
@@ -37150,7 +37147,7 @@
       <c r="N485" s="9"/>
       <c r="O485" s="9"/>
       <c r="P485" t="s" s="7">
-        <v>2430</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="486" ht="15.35" customHeight="1">
@@ -37173,10 +37170,10 @@
         <v>1247</v>
       </c>
       <c r="G486" t="s" s="7">
+        <v>2430</v>
+      </c>
+      <c r="H486" t="s" s="7">
         <v>2431</v>
-      </c>
-      <c r="H486" t="s" s="7">
-        <v>2432</v>
       </c>
       <c r="I486" t="s" s="7">
         <v>761</v>
@@ -37190,7 +37187,7 @@
       <c r="N486" s="9"/>
       <c r="O486" s="9"/>
       <c r="P486" t="s" s="7">
-        <v>2433</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="487" ht="15.35" customHeight="1">
@@ -37213,10 +37210,10 @@
         <v>1251</v>
       </c>
       <c r="G487" t="s" s="7">
+        <v>2433</v>
+      </c>
+      <c r="H487" t="s" s="7">
         <v>2434</v>
-      </c>
-      <c r="H487" t="s" s="7">
-        <v>2435</v>
       </c>
       <c r="I487" t="s" s="7">
         <v>254</v>
@@ -37230,7 +37227,7 @@
       <c r="N487" s="9"/>
       <c r="O487" s="9"/>
       <c r="P487" t="s" s="7">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="488" ht="15.35" customHeight="1">
@@ -37253,10 +37250,10 @@
         <v>1255</v>
       </c>
       <c r="G488" t="s" s="7">
+        <v>2436</v>
+      </c>
+      <c r="H488" t="s" s="7">
         <v>2437</v>
-      </c>
-      <c r="H488" t="s" s="7">
-        <v>2438</v>
       </c>
       <c r="I488" t="s" s="7">
         <v>87</v>
@@ -37270,7 +37267,7 @@
       <c r="N488" s="9"/>
       <c r="O488" s="9"/>
       <c r="P488" t="s" s="7">
-        <v>2439</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="489" ht="15.35" customHeight="1">
@@ -37293,13 +37290,13 @@
         <v>1259</v>
       </c>
       <c r="G489" t="s" s="7">
+        <v>2439</v>
+      </c>
+      <c r="H489" t="s" s="7">
         <v>2440</v>
       </c>
-      <c r="H489" t="s" s="7">
-        <v>2441</v>
-      </c>
       <c r="I489" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J489" t="s" s="7">
         <v>27</v>
@@ -37310,7 +37307,7 @@
       <c r="N489" s="9"/>
       <c r="O489" s="9"/>
       <c r="P489" t="s" s="7">
-        <v>2442</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="490" ht="15.35" customHeight="1">
@@ -37333,10 +37330,10 @@
         <v>1262</v>
       </c>
       <c r="G490" t="s" s="7">
+        <v>2442</v>
+      </c>
+      <c r="H490" t="s" s="7">
         <v>2443</v>
-      </c>
-      <c r="H490" t="s" s="7">
-        <v>2444</v>
       </c>
       <c r="I490" t="s" s="7">
         <v>704</v>
@@ -37350,7 +37347,7 @@
       <c r="N490" s="9"/>
       <c r="O490" s="9"/>
       <c r="P490" t="s" s="7">
-        <v>2445</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="491" ht="15.35" customHeight="1">
@@ -37373,7 +37370,7 @@
         <v>1266</v>
       </c>
       <c r="G491" t="s" s="7">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="H491" t="s" s="7">
         <v>769</v>
@@ -37390,7 +37387,7 @@
       <c r="N491" s="9"/>
       <c r="O491" s="9"/>
       <c r="P491" t="s" s="7">
-        <v>2447</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="492" ht="15.35" customHeight="1">
@@ -37413,13 +37410,13 @@
         <v>1617</v>
       </c>
       <c r="G492" t="s" s="7">
+        <v>2447</v>
+      </c>
+      <c r="H492" t="s" s="7">
         <v>2448</v>
       </c>
-      <c r="H492" t="s" s="7">
-        <v>2449</v>
-      </c>
       <c r="I492" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J492" t="s" s="7">
         <v>27</v>
@@ -37430,7 +37427,7 @@
       <c r="N492" s="9"/>
       <c r="O492" s="9"/>
       <c r="P492" t="s" s="7">
-        <v>2450</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="493" ht="15.35" customHeight="1">
@@ -37453,10 +37450,10 @@
         <v>1621</v>
       </c>
       <c r="G493" t="s" s="7">
+        <v>2450</v>
+      </c>
+      <c r="H493" t="s" s="7">
         <v>2451</v>
-      </c>
-      <c r="H493" t="s" s="7">
-        <v>2452</v>
       </c>
       <c r="I493" t="s" s="7">
         <v>803</v>
@@ -37470,7 +37467,7 @@
       <c r="N493" s="9"/>
       <c r="O493" s="9"/>
       <c r="P493" t="s" s="7">
-        <v>2453</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="494" ht="15.35" customHeight="1">
@@ -37493,13 +37490,13 @@
         <v>1625</v>
       </c>
       <c r="G494" t="s" s="7">
+        <v>2453</v>
+      </c>
+      <c r="H494" t="s" s="7">
         <v>2454</v>
       </c>
-      <c r="H494" t="s" s="7">
-        <v>2455</v>
-      </c>
       <c r="I494" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J494" t="s" s="7">
         <v>27</v>
@@ -37510,7 +37507,7 @@
       <c r="N494" s="9"/>
       <c r="O494" s="9"/>
       <c r="P494" t="s" s="7">
-        <v>2456</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="495" ht="15.35" customHeight="1">
@@ -37533,13 +37530,13 @@
         <v>1629</v>
       </c>
       <c r="G495" t="s" s="7">
+        <v>2456</v>
+      </c>
+      <c r="H495" t="s" s="7">
         <v>2457</v>
       </c>
-      <c r="H495" t="s" s="7">
-        <v>2458</v>
-      </c>
       <c r="I495" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J495" t="s" s="7">
         <v>27</v>
@@ -37550,7 +37547,7 @@
       <c r="N495" s="9"/>
       <c r="O495" s="9"/>
       <c r="P495" t="s" s="7">
-        <v>2459</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="496" ht="15.35" customHeight="1">
@@ -37573,10 +37570,10 @@
         <v>1633</v>
       </c>
       <c r="G496" t="s" s="7">
+        <v>2459</v>
+      </c>
+      <c r="H496" t="s" s="7">
         <v>2460</v>
-      </c>
-      <c r="H496" t="s" s="7">
-        <v>2461</v>
       </c>
       <c r="I496" t="s" s="7">
         <v>714</v>
@@ -37590,7 +37587,7 @@
       <c r="N496" s="9"/>
       <c r="O496" s="9"/>
       <c r="P496" t="s" s="7">
-        <v>2462</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="497" ht="15.35" customHeight="1">
@@ -37613,13 +37610,13 @@
         <v>1637</v>
       </c>
       <c r="G497" t="s" s="7">
+        <v>2462</v>
+      </c>
+      <c r="H497" t="s" s="7">
         <v>2463</v>
       </c>
-      <c r="H497" t="s" s="7">
-        <v>2464</v>
-      </c>
       <c r="I497" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J497" t="s" s="7">
         <v>27</v>
@@ -37630,7 +37627,7 @@
       <c r="N497" s="9"/>
       <c r="O497" s="9"/>
       <c r="P497" t="s" s="7">
-        <v>2465</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="498" ht="15.35" customHeight="1">
@@ -37653,10 +37650,10 @@
         <v>1641</v>
       </c>
       <c r="G498" t="s" s="7">
+        <v>2465</v>
+      </c>
+      <c r="H498" t="s" s="7">
         <v>2466</v>
-      </c>
-      <c r="H498" t="s" s="7">
-        <v>2467</v>
       </c>
       <c r="I498" t="s" s="7">
         <v>714</v>
@@ -37670,7 +37667,7 @@
       <c r="N498" s="9"/>
       <c r="O498" s="9"/>
       <c r="P498" t="s" s="7">
-        <v>2468</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="499" ht="15.35" customHeight="1">
@@ -37693,10 +37690,10 @@
         <v>1645</v>
       </c>
       <c r="G499" t="s" s="7">
+        <v>2468</v>
+      </c>
+      <c r="H499" t="s" s="7">
         <v>2469</v>
-      </c>
-      <c r="H499" t="s" s="7">
-        <v>2470</v>
       </c>
       <c r="I499" t="s" s="7">
         <v>714</v>
@@ -37710,7 +37707,7 @@
       <c r="N499" s="9"/>
       <c r="O499" s="9"/>
       <c r="P499" t="s" s="7">
-        <v>2471</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="500" ht="15.35" customHeight="1">
@@ -37733,10 +37730,10 @@
         <v>1649</v>
       </c>
       <c r="G500" t="s" s="7">
+        <v>2471</v>
+      </c>
+      <c r="H500" t="s" s="7">
         <v>2472</v>
-      </c>
-      <c r="H500" t="s" s="7">
-        <v>2473</v>
       </c>
       <c r="I500" t="s" s="7">
         <v>714</v>
@@ -37750,7 +37747,7 @@
       <c r="N500" s="9"/>
       <c r="O500" s="9"/>
       <c r="P500" t="s" s="7">
-        <v>2474</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="501" ht="15.35" customHeight="1">
@@ -37773,10 +37770,10 @@
         <v>1653</v>
       </c>
       <c r="G501" t="s" s="7">
+        <v>2474</v>
+      </c>
+      <c r="H501" t="s" s="7">
         <v>2475</v>
-      </c>
-      <c r="H501" t="s" s="7">
-        <v>2476</v>
       </c>
       <c r="I501" t="s" s="7">
         <v>714</v>
@@ -37790,7 +37787,7 @@
       <c r="N501" s="9"/>
       <c r="O501" s="9"/>
       <c r="P501" t="s" s="7">
-        <v>2477</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="502" ht="15.35" customHeight="1">
@@ -37813,10 +37810,10 @@
         <v>1657</v>
       </c>
       <c r="G502" t="s" s="7">
+        <v>2477</v>
+      </c>
+      <c r="H502" t="s" s="7">
         <v>2478</v>
-      </c>
-      <c r="H502" t="s" s="7">
-        <v>2479</v>
       </c>
       <c r="I502" t="s" s="7">
         <v>714</v>
@@ -37830,7 +37827,7 @@
       <c r="N502" s="9"/>
       <c r="O502" s="9"/>
       <c r="P502" t="s" s="7">
-        <v>2480</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="503" ht="15.35" customHeight="1">
@@ -37853,13 +37850,13 @@
         <v>1661</v>
       </c>
       <c r="G503" t="s" s="7">
+        <v>2480</v>
+      </c>
+      <c r="H503" t="s" s="7">
         <v>2481</v>
       </c>
-      <c r="H503" t="s" s="7">
-        <v>2482</v>
-      </c>
       <c r="I503" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J503" t="s" s="7">
         <v>27</v>
@@ -37870,7 +37867,7 @@
       <c r="N503" s="9"/>
       <c r="O503" s="9"/>
       <c r="P503" t="s" s="7">
-        <v>2483</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="504" ht="15.35" customHeight="1">
@@ -37893,10 +37890,10 @@
         <v>1665</v>
       </c>
       <c r="G504" t="s" s="7">
+        <v>2483</v>
+      </c>
+      <c r="H504" t="s" s="7">
         <v>2484</v>
-      </c>
-      <c r="H504" t="s" s="7">
-        <v>2485</v>
       </c>
       <c r="I504" t="s" s="7">
         <v>254</v>
@@ -37910,7 +37907,7 @@
       <c r="N504" s="9"/>
       <c r="O504" s="9"/>
       <c r="P504" t="s" s="7">
-        <v>2486</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="505" ht="15.35" customHeight="1">
@@ -37933,10 +37930,10 @@
         <v>1669</v>
       </c>
       <c r="G505" t="s" s="7">
+        <v>2486</v>
+      </c>
+      <c r="H505" t="s" s="7">
         <v>2487</v>
-      </c>
-      <c r="H505" t="s" s="7">
-        <v>2488</v>
       </c>
       <c r="I505" t="s" s="7">
         <v>254</v>
@@ -37950,7 +37947,7 @@
       <c r="N505" s="9"/>
       <c r="O505" s="9"/>
       <c r="P505" t="s" s="7">
-        <v>2489</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="506" ht="15.35" customHeight="1">
@@ -37970,13 +37967,13 @@
         <v>793</v>
       </c>
       <c r="F506" t="s" s="7">
+        <v>2489</v>
+      </c>
+      <c r="G506" t="s" s="7">
         <v>2490</v>
       </c>
-      <c r="G506" t="s" s="7">
+      <c r="H506" t="s" s="7">
         <v>2491</v>
-      </c>
-      <c r="H506" t="s" s="7">
-        <v>2492</v>
       </c>
       <c r="I506" t="s" s="7">
         <v>714</v>
@@ -37990,7 +37987,7 @@
       <c r="N506" s="9"/>
       <c r="O506" s="9"/>
       <c r="P506" t="s" s="7">
-        <v>2493</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="507" ht="15.35" customHeight="1">
@@ -38010,13 +38007,13 @@
         <v>793</v>
       </c>
       <c r="F507" t="s" s="7">
+        <v>2493</v>
+      </c>
+      <c r="G507" t="s" s="7">
         <v>2494</v>
       </c>
-      <c r="G507" t="s" s="7">
+      <c r="H507" t="s" s="7">
         <v>2495</v>
-      </c>
-      <c r="H507" t="s" s="7">
-        <v>2496</v>
       </c>
       <c r="I507" t="s" s="7">
         <v>714</v>
@@ -38030,7 +38027,7 @@
       <c r="N507" s="9"/>
       <c r="O507" s="9"/>
       <c r="P507" t="s" s="7">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="508" ht="15.35" customHeight="1">
@@ -38050,13 +38047,13 @@
         <v>793</v>
       </c>
       <c r="F508" t="s" s="7">
+        <v>2497</v>
+      </c>
+      <c r="G508" t="s" s="7">
         <v>2498</v>
       </c>
-      <c r="G508" t="s" s="7">
+      <c r="H508" t="s" s="7">
         <v>2499</v>
-      </c>
-      <c r="H508" t="s" s="7">
-        <v>2500</v>
       </c>
       <c r="I508" t="s" s="7">
         <v>714</v>
@@ -38070,7 +38067,7 @@
       <c r="N508" s="9"/>
       <c r="O508" s="9"/>
       <c r="P508" t="s" s="7">
-        <v>2501</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="509" ht="15.35" customHeight="1">
@@ -38090,13 +38087,13 @@
         <v>793</v>
       </c>
       <c r="F509" t="s" s="7">
+        <v>2501</v>
+      </c>
+      <c r="G509" t="s" s="7">
         <v>2502</v>
       </c>
-      <c r="G509" t="s" s="7">
+      <c r="H509" t="s" s="7">
         <v>2503</v>
-      </c>
-      <c r="H509" t="s" s="7">
-        <v>2504</v>
       </c>
       <c r="I509" t="s" s="7">
         <v>254</v>
@@ -38110,7 +38107,7 @@
       <c r="N509" s="9"/>
       <c r="O509" s="9"/>
       <c r="P509" t="s" s="7">
-        <v>2505</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="510" ht="15.35" customHeight="1">
@@ -38130,13 +38127,13 @@
         <v>797</v>
       </c>
       <c r="F510" t="s" s="7">
+        <v>2505</v>
+      </c>
+      <c r="G510" t="s" s="7">
         <v>2506</v>
       </c>
-      <c r="G510" t="s" s="7">
+      <c r="H510" t="s" s="7">
         <v>2507</v>
-      </c>
-      <c r="H510" t="s" s="7">
-        <v>2508</v>
       </c>
       <c r="I510" t="s" s="7">
         <v>714</v>
@@ -38150,7 +38147,7 @@
       <c r="N510" s="9"/>
       <c r="O510" s="9"/>
       <c r="P510" t="s" s="7">
-        <v>2509</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="511" ht="15.35" customHeight="1">
@@ -38170,13 +38167,13 @@
         <v>797</v>
       </c>
       <c r="F511" t="s" s="7">
+        <v>2509</v>
+      </c>
+      <c r="G511" t="s" s="7">
         <v>2510</v>
       </c>
-      <c r="G511" t="s" s="7">
+      <c r="H511" t="s" s="7">
         <v>2511</v>
-      </c>
-      <c r="H511" t="s" s="7">
-        <v>2512</v>
       </c>
       <c r="I511" t="s" s="7">
         <v>714</v>
@@ -38190,7 +38187,7 @@
       <c r="N511" s="9"/>
       <c r="O511" s="9"/>
       <c r="P511" t="s" s="7">
-        <v>2513</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="512" ht="15.35" customHeight="1">
@@ -38210,13 +38207,13 @@
         <v>797</v>
       </c>
       <c r="F512" t="s" s="7">
+        <v>2513</v>
+      </c>
+      <c r="G512" t="s" s="7">
         <v>2514</v>
       </c>
-      <c r="G512" t="s" s="7">
+      <c r="H512" t="s" s="7">
         <v>2515</v>
-      </c>
-      <c r="H512" t="s" s="7">
-        <v>2516</v>
       </c>
       <c r="I512" t="s" s="7">
         <v>714</v>
@@ -38230,7 +38227,7 @@
       <c r="N512" s="9"/>
       <c r="O512" s="9"/>
       <c r="P512" t="s" s="7">
-        <v>2517</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="513" ht="15.35" customHeight="1">
@@ -38250,16 +38247,16 @@
         <v>801</v>
       </c>
       <c r="F513" t="s" s="7">
+        <v>2517</v>
+      </c>
+      <c r="G513" t="s" s="7">
         <v>2518</v>
       </c>
-      <c r="G513" t="s" s="7">
+      <c r="H513" t="s" s="7">
         <v>2519</v>
       </c>
-      <c r="H513" t="s" s="7">
-        <v>2520</v>
-      </c>
       <c r="I513" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J513" t="s" s="7">
         <v>27</v>
@@ -38270,7 +38267,7 @@
       <c r="N513" s="9"/>
       <c r="O513" s="9"/>
       <c r="P513" t="s" s="7">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="514" ht="15.35" customHeight="1">
@@ -38290,16 +38287,16 @@
         <v>801</v>
       </c>
       <c r="F514" t="s" s="7">
+        <v>2521</v>
+      </c>
+      <c r="G514" t="s" s="7">
         <v>2522</v>
       </c>
-      <c r="G514" t="s" s="7">
+      <c r="H514" t="s" s="7">
         <v>2523</v>
       </c>
-      <c r="H514" t="s" s="7">
-        <v>2524</v>
-      </c>
       <c r="I514" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J514" t="s" s="7">
         <v>27</v>
@@ -38310,7 +38307,7 @@
       <c r="N514" s="9"/>
       <c r="O514" s="9"/>
       <c r="P514" t="s" s="7">
-        <v>2525</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="515" ht="15.35" customHeight="1">
@@ -38330,13 +38327,13 @@
         <v>801</v>
       </c>
       <c r="F515" t="s" s="7">
+        <v>2525</v>
+      </c>
+      <c r="G515" t="s" s="7">
         <v>2526</v>
       </c>
-      <c r="G515" t="s" s="7">
+      <c r="H515" t="s" s="7">
         <v>2527</v>
-      </c>
-      <c r="H515" t="s" s="7">
-        <v>2528</v>
       </c>
       <c r="I515" t="s" s="7">
         <v>714</v>
@@ -38350,7 +38347,7 @@
       <c r="N515" s="9"/>
       <c r="O515" s="9"/>
       <c r="P515" t="s" s="7">
-        <v>2529</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="516" ht="15.35" customHeight="1">
@@ -38370,13 +38367,13 @@
         <v>806</v>
       </c>
       <c r="F516" t="s" s="7">
+        <v>2529</v>
+      </c>
+      <c r="G516" t="s" s="7">
         <v>2530</v>
       </c>
-      <c r="G516" t="s" s="7">
+      <c r="H516" t="s" s="7">
         <v>2531</v>
-      </c>
-      <c r="H516" t="s" s="7">
-        <v>2532</v>
       </c>
       <c r="I516" t="s" s="7">
         <v>704</v>
@@ -38390,7 +38387,7 @@
       <c r="N516" s="9"/>
       <c r="O516" s="9"/>
       <c r="P516" t="s" s="7">
-        <v>2533</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="517" ht="15.35" customHeight="1">
@@ -38410,16 +38407,16 @@
         <v>806</v>
       </c>
       <c r="F517" t="s" s="7">
+        <v>2533</v>
+      </c>
+      <c r="G517" t="s" s="7">
         <v>2534</v>
       </c>
-      <c r="G517" t="s" s="7">
+      <c r="H517" t="s" s="7">
         <v>2535</v>
       </c>
-      <c r="H517" t="s" s="7">
-        <v>2536</v>
-      </c>
       <c r="I517" t="s" s="7">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="J517" t="s" s="7">
         <v>27</v>
@@ -38430,7 +38427,7 @@
       <c r="N517" s="9"/>
       <c r="O517" s="9"/>
       <c r="P517" t="s" s="7">
-        <v>2537</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="518" ht="15.35" customHeight="1">
@@ -38450,13 +38447,13 @@
         <v>806</v>
       </c>
       <c r="F518" t="s" s="7">
+        <v>2537</v>
+      </c>
+      <c r="G518" t="s" s="7">
         <v>2538</v>
       </c>
-      <c r="G518" t="s" s="7">
+      <c r="H518" t="s" s="7">
         <v>2539</v>
-      </c>
-      <c r="H518" t="s" s="7">
-        <v>2540</v>
       </c>
       <c r="I518" t="s" s="7">
         <v>714</v>
@@ -38470,7 +38467,7 @@
       <c r="N518" s="9"/>
       <c r="O518" s="9"/>
       <c r="P518" t="s" s="7">
-        <v>2541</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="519" ht="15.35" customHeight="1">
@@ -38490,13 +38487,13 @@
         <v>806</v>
       </c>
       <c r="F519" t="s" s="7">
+        <v>2541</v>
+      </c>
+      <c r="G519" t="s" s="7">
         <v>2542</v>
       </c>
-      <c r="G519" t="s" s="7">
+      <c r="H519" t="s" s="7">
         <v>2543</v>
-      </c>
-      <c r="H519" t="s" s="7">
-        <v>2544</v>
       </c>
       <c r="I519" t="s" s="7">
         <v>714</v>
@@ -38510,7 +38507,7 @@
       <c r="N519" s="9"/>
       <c r="O519" s="9"/>
       <c r="P519" t="s" s="7">
-        <v>2545</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="520" ht="15.35" customHeight="1">
@@ -38533,10 +38530,10 @@
         <v>940</v>
       </c>
       <c r="G520" t="s" s="7">
+        <v>2545</v>
+      </c>
+      <c r="H520" t="s" s="7">
         <v>2546</v>
-      </c>
-      <c r="H520" t="s" s="7">
-        <v>2547</v>
       </c>
       <c r="I520" t="s" s="7">
         <v>842</v>
@@ -38550,7 +38547,7 @@
       <c r="N520" s="9"/>
       <c r="O520" s="9"/>
       <c r="P520" t="s" s="7">
-        <v>2548</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="521" ht="15.35" customHeight="1">
@@ -38573,10 +38570,10 @@
         <v>944</v>
       </c>
       <c r="G521" t="s" s="7">
+        <v>2548</v>
+      </c>
+      <c r="H521" t="s" s="7">
         <v>2549</v>
-      </c>
-      <c r="H521" t="s" s="7">
-        <v>2550</v>
       </c>
       <c r="I521" t="s" s="7">
         <v>917</v>
@@ -38590,7 +38587,7 @@
       <c r="N521" s="9"/>
       <c r="O521" s="9"/>
       <c r="P521" t="s" s="7">
-        <v>2551</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="522" ht="15.35" customHeight="1">
@@ -38613,10 +38610,10 @@
         <v>948</v>
       </c>
       <c r="G522" t="s" s="7">
+        <v>2551</v>
+      </c>
+      <c r="H522" t="s" s="7">
         <v>2552</v>
-      </c>
-      <c r="H522" t="s" s="7">
-        <v>2553</v>
       </c>
       <c r="I522" t="s" s="7">
         <v>817</v>
@@ -38630,7 +38627,7 @@
       <c r="N522" s="9"/>
       <c r="O522" s="9"/>
       <c r="P522" t="s" s="7">
-        <v>2554</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="523" ht="15.35" customHeight="1">
@@ -38653,10 +38650,10 @@
         <v>952</v>
       </c>
       <c r="G523" t="s" s="7">
+        <v>2554</v>
+      </c>
+      <c r="H523" t="s" s="7">
         <v>2555</v>
-      </c>
-      <c r="H523" t="s" s="7">
-        <v>2556</v>
       </c>
       <c r="I523" t="s" s="7">
         <v>817</v>
@@ -38670,7 +38667,7 @@
       <c r="N523" s="9"/>
       <c r="O523" s="9"/>
       <c r="P523" t="s" s="7">
-        <v>2557</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="524" ht="15.35" customHeight="1">
@@ -38693,10 +38690,10 @@
         <v>956</v>
       </c>
       <c r="G524" t="s" s="7">
+        <v>2557</v>
+      </c>
+      <c r="H524" t="s" s="7">
         <v>2558</v>
-      </c>
-      <c r="H524" t="s" s="7">
-        <v>2559</v>
       </c>
       <c r="I524" t="s" s="7">
         <v>817</v>
@@ -38710,7 +38707,7 @@
       <c r="N524" s="9"/>
       <c r="O524" s="9"/>
       <c r="P524" t="s" s="7">
-        <v>2560</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="525" ht="15.35" customHeight="1">
@@ -38733,10 +38730,10 @@
         <v>960</v>
       </c>
       <c r="G525" t="s" s="7">
+        <v>2560</v>
+      </c>
+      <c r="H525" t="s" s="7">
         <v>2561</v>
-      </c>
-      <c r="H525" t="s" s="7">
-        <v>2562</v>
       </c>
       <c r="I525" t="s" s="7">
         <v>817</v>
@@ -38750,7 +38747,7 @@
       <c r="N525" s="9"/>
       <c r="O525" s="9"/>
       <c r="P525" t="s" s="7">
-        <v>2563</v>
+        <v>2562</v>
       </c>
     </row>
     <row r="526" ht="15.35" customHeight="1">
@@ -38773,10 +38770,10 @@
         <v>964</v>
       </c>
       <c r="G526" t="s" s="7">
+        <v>2563</v>
+      </c>
+      <c r="H526" t="s" s="7">
         <v>2564</v>
-      </c>
-      <c r="H526" t="s" s="7">
-        <v>2565</v>
       </c>
       <c r="I526" t="s" s="7">
         <v>817</v>
@@ -38790,7 +38787,7 @@
       <c r="N526" s="9"/>
       <c r="O526" s="9"/>
       <c r="P526" t="s" s="7">
-        <v>2566</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="527" ht="15.35" customHeight="1">
@@ -38813,10 +38810,10 @@
         <v>968</v>
       </c>
       <c r="G527" t="s" s="7">
+        <v>2566</v>
+      </c>
+      <c r="H527" t="s" s="7">
         <v>2567</v>
-      </c>
-      <c r="H527" t="s" s="7">
-        <v>2568</v>
       </c>
       <c r="I527" t="s" s="7">
         <v>817</v>
@@ -38830,7 +38827,7 @@
       <c r="N527" s="9"/>
       <c r="O527" s="9"/>
       <c r="P527" t="s" s="7">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="528" ht="15.35" customHeight="1">
@@ -38853,7 +38850,7 @@
         <v>972</v>
       </c>
       <c r="G528" t="s" s="7">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="H528" t="s" s="7">
         <v>829</v>
@@ -38870,7 +38867,7 @@
       <c r="N528" s="9"/>
       <c r="O528" s="9"/>
       <c r="P528" t="s" s="7">
-        <v>2571</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="529" ht="15.35" customHeight="1">
@@ -38893,10 +38890,10 @@
         <v>976</v>
       </c>
       <c r="G529" t="s" s="7">
+        <v>2571</v>
+      </c>
+      <c r="H529" t="s" s="7">
         <v>2572</v>
-      </c>
-      <c r="H529" t="s" s="7">
-        <v>2573</v>
       </c>
       <c r="I529" t="s" s="7">
         <v>204</v>
@@ -38910,7 +38907,7 @@
       <c r="N529" s="9"/>
       <c r="O529" s="9"/>
       <c r="P529" t="s" s="7">
-        <v>2574</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="530" ht="15.35" customHeight="1">
@@ -38933,13 +38930,13 @@
         <v>980</v>
       </c>
       <c r="G530" t="s" s="7">
+        <v>2574</v>
+      </c>
+      <c r="H530" t="s" s="7">
         <v>2575</v>
       </c>
-      <c r="H530" t="s" s="7">
+      <c r="I530" t="s" s="7">
         <v>2576</v>
-      </c>
-      <c r="I530" t="s" s="7">
-        <v>2577</v>
       </c>
       <c r="J530" t="s" s="7">
         <v>27</v>
@@ -38950,7 +38947,7 @@
       <c r="N530" s="9"/>
       <c r="O530" s="9"/>
       <c r="P530" t="s" s="7">
-        <v>2578</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="531" ht="15.35" customHeight="1">
@@ -38973,10 +38970,10 @@
         <v>984</v>
       </c>
       <c r="G531" t="s" s="7">
+        <v>2578</v>
+      </c>
+      <c r="H531" t="s" s="7">
         <v>2579</v>
-      </c>
-      <c r="H531" t="s" s="7">
-        <v>2580</v>
       </c>
       <c r="I531" t="s" s="7">
         <v>842</v>
@@ -38990,7 +38987,7 @@
       <c r="N531" s="9"/>
       <c r="O531" s="9"/>
       <c r="P531" t="s" s="7">
-        <v>2581</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="532" ht="15.35" customHeight="1">
@@ -39013,10 +39010,10 @@
         <v>988</v>
       </c>
       <c r="G532" t="s" s="7">
+        <v>2581</v>
+      </c>
+      <c r="H532" t="s" s="7">
         <v>2582</v>
-      </c>
-      <c r="H532" t="s" s="7">
-        <v>2583</v>
       </c>
       <c r="I532" t="s" s="7">
         <v>842</v>
@@ -39030,7 +39027,7 @@
       <c r="N532" s="9"/>
       <c r="O532" s="9"/>
       <c r="P532" t="s" s="7">
-        <v>2584</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="533" ht="15.35" customHeight="1">
@@ -39053,10 +39050,10 @@
         <v>992</v>
       </c>
       <c r="G533" t="s" s="7">
+        <v>2584</v>
+      </c>
+      <c r="H533" t="s" s="7">
         <v>2585</v>
-      </c>
-      <c r="H533" t="s" s="7">
-        <v>2586</v>
       </c>
       <c r="I533" t="s" s="7">
         <v>842</v>
@@ -39070,7 +39067,7 @@
       <c r="N533" s="9"/>
       <c r="O533" s="9"/>
       <c r="P533" t="s" s="7">
-        <v>2587</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="534" ht="15.35" customHeight="1">
@@ -39093,10 +39090,10 @@
         <v>996</v>
       </c>
       <c r="G534" t="s" s="7">
+        <v>2587</v>
+      </c>
+      <c r="H534" t="s" s="7">
         <v>2588</v>
-      </c>
-      <c r="H534" t="s" s="7">
-        <v>2589</v>
       </c>
       <c r="I534" t="s" s="7">
         <v>817</v>
@@ -39110,7 +39107,7 @@
       <c r="N534" s="9"/>
       <c r="O534" s="9"/>
       <c r="P534" t="s" s="7">
-        <v>2590</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="535" ht="15.35" customHeight="1">
@@ -39133,10 +39130,10 @@
         <v>1044</v>
       </c>
       <c r="G535" t="s" s="7">
+        <v>2590</v>
+      </c>
+      <c r="H535" t="s" s="7">
         <v>2591</v>
-      </c>
-      <c r="H535" t="s" s="7">
-        <v>2592</v>
       </c>
       <c r="I535" t="s" s="7">
         <v>817</v>
@@ -39150,7 +39147,7 @@
       <c r="N535" s="9"/>
       <c r="O535" s="9"/>
       <c r="P535" t="s" s="7">
-        <v>2593</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="536" ht="15.35" customHeight="1">
@@ -39173,10 +39170,10 @@
         <v>1048</v>
       </c>
       <c r="G536" t="s" s="7">
+        <v>2593</v>
+      </c>
+      <c r="H536" t="s" s="7">
         <v>2594</v>
-      </c>
-      <c r="H536" t="s" s="7">
-        <v>2595</v>
       </c>
       <c r="I536" t="s" s="7">
         <v>817</v>
@@ -39190,7 +39187,7 @@
       <c r="N536" s="9"/>
       <c r="O536" s="9"/>
       <c r="P536" t="s" s="7">
-        <v>2596</v>
+        <v>2595</v>
       </c>
     </row>
     <row r="537" ht="15.35" customHeight="1">
@@ -39213,10 +39210,10 @@
         <v>1052</v>
       </c>
       <c r="G537" t="s" s="7">
+        <v>2596</v>
+      </c>
+      <c r="H537" t="s" s="7">
         <v>2597</v>
-      </c>
-      <c r="H537" t="s" s="7">
-        <v>2598</v>
       </c>
       <c r="I537" t="s" s="7">
         <v>817</v>
@@ -39230,7 +39227,7 @@
       <c r="N537" s="9"/>
       <c r="O537" s="9"/>
       <c r="P537" t="s" s="7">
-        <v>2599</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="538" ht="15.35" customHeight="1">
@@ -39253,10 +39250,10 @@
         <v>1056</v>
       </c>
       <c r="G538" t="s" s="7">
+        <v>2599</v>
+      </c>
+      <c r="H538" t="s" s="7">
         <v>2600</v>
-      </c>
-      <c r="H538" t="s" s="7">
-        <v>2601</v>
       </c>
       <c r="I538" t="s" s="7">
         <v>817</v>
@@ -39270,7 +39267,7 @@
       <c r="N538" s="9"/>
       <c r="O538" s="9"/>
       <c r="P538" t="s" s="7">
-        <v>2602</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="539" ht="15.35" customHeight="1">
@@ -39293,10 +39290,10 @@
         <v>1060</v>
       </c>
       <c r="G539" t="s" s="7">
+        <v>2602</v>
+      </c>
+      <c r="H539" t="s" s="7">
         <v>2603</v>
-      </c>
-      <c r="H539" t="s" s="7">
-        <v>2604</v>
       </c>
       <c r="I539" t="s" s="7">
         <v>817</v>
@@ -39310,7 +39307,7 @@
       <c r="N539" s="9"/>
       <c r="O539" s="9"/>
       <c r="P539" t="s" s="7">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="540" ht="15.35" customHeight="1">
@@ -39333,10 +39330,10 @@
         <v>1064</v>
       </c>
       <c r="G540" t="s" s="7">
+        <v>2605</v>
+      </c>
+      <c r="H540" t="s" s="7">
         <v>2606</v>
-      </c>
-      <c r="H540" t="s" s="7">
-        <v>2607</v>
       </c>
       <c r="I540" t="s" s="7">
         <v>817</v>
@@ -39350,7 +39347,7 @@
       <c r="N540" s="9"/>
       <c r="O540" s="9"/>
       <c r="P540" t="s" s="7">
-        <v>2608</v>
+        <v>2607</v>
       </c>
     </row>
     <row r="541" ht="15.35" customHeight="1">
@@ -39373,10 +39370,10 @@
         <v>1068</v>
       </c>
       <c r="G541" t="s" s="7">
+        <v>2608</v>
+      </c>
+      <c r="H541" t="s" s="7">
         <v>2609</v>
-      </c>
-      <c r="H541" t="s" s="7">
-        <v>2610</v>
       </c>
       <c r="I541" t="s" s="7">
         <v>817</v>
@@ -39390,7 +39387,7 @@
       <c r="N541" s="9"/>
       <c r="O541" s="9"/>
       <c r="P541" t="s" s="7">
-        <v>2611</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="542" ht="15.35" customHeight="1">
@@ -39413,10 +39410,10 @@
         <v>1072</v>
       </c>
       <c r="G542" t="s" s="7">
+        <v>2611</v>
+      </c>
+      <c r="H542" t="s" s="7">
         <v>2612</v>
-      </c>
-      <c r="H542" t="s" s="7">
-        <v>2613</v>
       </c>
       <c r="I542" t="s" s="7">
         <v>817</v>
@@ -39430,7 +39427,7 @@
       <c r="N542" s="9"/>
       <c r="O542" s="9"/>
       <c r="P542" t="s" s="7">
-        <v>2614</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="543" ht="15.35" customHeight="1">
@@ -39453,10 +39450,10 @@
         <v>1076</v>
       </c>
       <c r="G543" t="s" s="7">
+        <v>2614</v>
+      </c>
+      <c r="H543" t="s" s="7">
         <v>2615</v>
-      </c>
-      <c r="H543" t="s" s="7">
-        <v>2616</v>
       </c>
       <c r="I543" t="s" s="7">
         <v>817</v>
@@ -39470,7 +39467,7 @@
       <c r="N543" s="9"/>
       <c r="O543" s="9"/>
       <c r="P543" t="s" s="7">
-        <v>2617</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="544" ht="15.35" customHeight="1">
@@ -39493,10 +39490,10 @@
         <v>1080</v>
       </c>
       <c r="G544" t="s" s="7">
+        <v>2617</v>
+      </c>
+      <c r="H544" t="s" s="7">
         <v>2618</v>
-      </c>
-      <c r="H544" t="s" s="7">
-        <v>2619</v>
       </c>
       <c r="I544" t="s" s="7">
         <v>817</v>
@@ -39510,7 +39507,7 @@
       <c r="N544" s="9"/>
       <c r="O544" s="9"/>
       <c r="P544" t="s" s="7">
-        <v>2620</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="545" ht="15.35" customHeight="1">
@@ -39533,10 +39530,10 @@
         <v>1084</v>
       </c>
       <c r="G545" t="s" s="7">
+        <v>2620</v>
+      </c>
+      <c r="H545" t="s" s="7">
         <v>2621</v>
-      </c>
-      <c r="H545" t="s" s="7">
-        <v>2622</v>
       </c>
       <c r="I545" t="s" s="7">
         <v>817</v>
@@ -39550,7 +39547,7 @@
       <c r="N545" s="9"/>
       <c r="O545" s="9"/>
       <c r="P545" t="s" s="7">
-        <v>2623</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="546" ht="15.35" customHeight="1">
@@ -39573,10 +39570,10 @@
         <v>1088</v>
       </c>
       <c r="G546" t="s" s="7">
+        <v>2623</v>
+      </c>
+      <c r="H546" t="s" s="7">
         <v>2624</v>
-      </c>
-      <c r="H546" t="s" s="7">
-        <v>2625</v>
       </c>
       <c r="I546" t="s" s="7">
         <v>817</v>
@@ -39590,7 +39587,7 @@
       <c r="N546" s="9"/>
       <c r="O546" s="9"/>
       <c r="P546" t="s" s="7">
-        <v>2626</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="547" ht="15.35" customHeight="1">
@@ -39613,10 +39610,10 @@
         <v>1092</v>
       </c>
       <c r="G547" t="s" s="7">
+        <v>2626</v>
+      </c>
+      <c r="H547" t="s" s="7">
         <v>2627</v>
-      </c>
-      <c r="H547" t="s" s="7">
-        <v>2628</v>
       </c>
       <c r="I547" t="s" s="7">
         <v>817</v>
@@ -39630,7 +39627,7 @@
       <c r="N547" s="9"/>
       <c r="O547" s="9"/>
       <c r="P547" t="s" s="7">
-        <v>2629</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="548" ht="15.35" customHeight="1">
@@ -39653,10 +39650,10 @@
         <v>1096</v>
       </c>
       <c r="G548" t="s" s="7">
+        <v>2629</v>
+      </c>
+      <c r="H548" t="s" s="7">
         <v>2630</v>
-      </c>
-      <c r="H548" t="s" s="7">
-        <v>2631</v>
       </c>
       <c r="I548" t="s" s="7">
         <v>817</v>
@@ -39670,7 +39667,7 @@
       <c r="N548" s="9"/>
       <c r="O548" s="9"/>
       <c r="P548" t="s" s="7">
-        <v>2632</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="549" ht="15.35" customHeight="1">
@@ -39693,10 +39690,10 @@
         <v>1100</v>
       </c>
       <c r="G549" t="s" s="7">
+        <v>2632</v>
+      </c>
+      <c r="H549" t="s" s="7">
         <v>2633</v>
-      </c>
-      <c r="H549" t="s" s="7">
-        <v>2634</v>
       </c>
       <c r="I549" t="s" s="7">
         <v>855</v>
@@ -39710,7 +39707,7 @@
       <c r="N549" s="9"/>
       <c r="O549" s="9"/>
       <c r="P549" t="s" s="7">
-        <v>2635</v>
+        <v>2634</v>
       </c>
     </row>
     <row r="550" ht="15.35" customHeight="1">
@@ -39733,10 +39730,10 @@
         <v>1104</v>
       </c>
       <c r="G550" t="s" s="7">
+        <v>2635</v>
+      </c>
+      <c r="H550" t="s" s="7">
         <v>2636</v>
-      </c>
-      <c r="H550" t="s" s="7">
-        <v>2637</v>
       </c>
       <c r="I550" t="s" s="7">
         <v>855</v>
@@ -39750,7 +39747,7 @@
       <c r="N550" s="9"/>
       <c r="O550" s="9"/>
       <c r="P550" t="s" s="7">
-        <v>2638</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="551" ht="15.35" customHeight="1">
@@ -39773,10 +39770,10 @@
         <v>1108</v>
       </c>
       <c r="G551" t="s" s="7">
+        <v>2638</v>
+      </c>
+      <c r="H551" t="s" s="7">
         <v>2639</v>
-      </c>
-      <c r="H551" t="s" s="7">
-        <v>2640</v>
       </c>
       <c r="I551" t="s" s="7">
         <v>842</v>
@@ -39790,7 +39787,7 @@
       <c r="N551" s="9"/>
       <c r="O551" s="9"/>
       <c r="P551" t="s" s="7">
-        <v>2641</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="552" ht="15.35" customHeight="1">
@@ -39813,13 +39810,13 @@
         <v>1112</v>
       </c>
       <c r="G552" t="s" s="7">
+        <v>2641</v>
+      </c>
+      <c r="H552" t="s" s="7">
         <v>2642</v>
       </c>
-      <c r="H552" t="s" s="7">
-        <v>2643</v>
-      </c>
       <c r="I552" t="s" s="7">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="J552" t="s" s="7">
         <v>27</v>
@@ -39830,7 +39827,7 @@
       <c r="N552" s="9"/>
       <c r="O552" s="9"/>
       <c r="P552" t="s" s="7">
-        <v>2644</v>
+        <v>2643</v>
       </c>
     </row>
     <row r="553" ht="15.35" customHeight="1">
@@ -39853,10 +39850,10 @@
         <v>1116</v>
       </c>
       <c r="G553" t="s" s="7">
+        <v>2644</v>
+      </c>
+      <c r="H553" t="s" s="7">
         <v>2645</v>
-      </c>
-      <c r="H553" t="s" s="7">
-        <v>2646</v>
       </c>
       <c r="I553" t="s" s="7">
         <v>855</v>
@@ -39870,7 +39867,7 @@
       <c r="N553" s="9"/>
       <c r="O553" s="9"/>
       <c r="P553" t="s" s="7">
-        <v>2647</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="554" ht="15.35" customHeight="1">
@@ -39893,10 +39890,10 @@
         <v>1120</v>
       </c>
       <c r="G554" t="s" s="7">
+        <v>2647</v>
+      </c>
+      <c r="H554" t="s" s="7">
         <v>2648</v>
-      </c>
-      <c r="H554" t="s" s="7">
-        <v>2649</v>
       </c>
       <c r="I554" t="s" s="7">
         <v>817</v>
@@ -39910,7 +39907,7 @@
       <c r="N554" s="9"/>
       <c r="O554" s="9"/>
       <c r="P554" t="s" s="7">
-        <v>2650</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="555" ht="15.35" customHeight="1">
@@ -39933,10 +39930,10 @@
         <v>1125</v>
       </c>
       <c r="G555" t="s" s="7">
+        <v>2650</v>
+      </c>
+      <c r="H555" t="s" s="7">
         <v>2651</v>
-      </c>
-      <c r="H555" t="s" s="7">
-        <v>2652</v>
       </c>
       <c r="I555" t="s" s="7">
         <v>817</v>
@@ -39950,7 +39947,7 @@
       <c r="N555" s="9"/>
       <c r="O555" s="9"/>
       <c r="P555" t="s" s="7">
-        <v>2653</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="556" ht="15.35" customHeight="1">
@@ -39973,10 +39970,10 @@
         <v>1235</v>
       </c>
       <c r="G556" t="s" s="7">
+        <v>2653</v>
+      </c>
+      <c r="H556" t="s" s="7">
         <v>2654</v>
-      </c>
-      <c r="H556" t="s" s="7">
-        <v>2655</v>
       </c>
       <c r="I556" t="s" s="7">
         <v>817</v>
@@ -39990,7 +39987,7 @@
       <c r="N556" s="9"/>
       <c r="O556" s="9"/>
       <c r="P556" t="s" s="7">
-        <v>2656</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="557" ht="15.35" customHeight="1">
@@ -40013,10 +40010,10 @@
         <v>1239</v>
       </c>
       <c r="G557" t="s" s="7">
+        <v>2656</v>
+      </c>
+      <c r="H557" t="s" s="7">
         <v>2657</v>
-      </c>
-      <c r="H557" t="s" s="7">
-        <v>2658</v>
       </c>
       <c r="I557" t="s" s="7">
         <v>817</v>
@@ -40030,7 +40027,7 @@
       <c r="N557" s="9"/>
       <c r="O557" s="9"/>
       <c r="P557" t="s" s="7">
-        <v>2659</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="558" ht="15.35" customHeight="1">
@@ -40053,10 +40050,10 @@
         <v>1243</v>
       </c>
       <c r="G558" t="s" s="7">
+        <v>2659</v>
+      </c>
+      <c r="H558" t="s" s="7">
         <v>2660</v>
-      </c>
-      <c r="H558" t="s" s="7">
-        <v>2661</v>
       </c>
       <c r="I558" t="s" s="7">
         <v>917</v>
@@ -40070,7 +40067,7 @@
       <c r="N558" s="9"/>
       <c r="O558" s="9"/>
       <c r="P558" t="s" s="7">
-        <v>2662</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="559" ht="15.35" customHeight="1">
@@ -40093,10 +40090,10 @@
         <v>1247</v>
       </c>
       <c r="G559" t="s" s="7">
+        <v>2662</v>
+      </c>
+      <c r="H559" t="s" s="7">
         <v>2663</v>
-      </c>
-      <c r="H559" t="s" s="7">
-        <v>2664</v>
       </c>
       <c r="I559" t="s" s="7">
         <v>817</v>
@@ -40110,7 +40107,7 @@
       <c r="N559" s="9"/>
       <c r="O559" s="9"/>
       <c r="P559" t="s" s="7">
-        <v>2665</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="560" ht="15.35" customHeight="1">
@@ -40133,10 +40130,10 @@
         <v>1251</v>
       </c>
       <c r="G560" t="s" s="7">
+        <v>2665</v>
+      </c>
+      <c r="H560" t="s" s="7">
         <v>2666</v>
-      </c>
-      <c r="H560" t="s" s="7">
-        <v>2667</v>
       </c>
       <c r="I560" t="s" s="7">
         <v>817</v>
@@ -40150,7 +40147,7 @@
       <c r="N560" s="9"/>
       <c r="O560" s="9"/>
       <c r="P560" t="s" s="7">
-        <v>2668</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="561" ht="15.35" customHeight="1">
@@ -40173,10 +40170,10 @@
         <v>1255</v>
       </c>
       <c r="G561" t="s" s="7">
+        <v>2668</v>
+      </c>
+      <c r="H561" t="s" s="7">
         <v>2669</v>
-      </c>
-      <c r="H561" t="s" s="7">
-        <v>2670</v>
       </c>
       <c r="I561" t="s" s="7">
         <v>817</v>
@@ -40190,7 +40187,7 @@
       <c r="N561" s="9"/>
       <c r="O561" s="9"/>
       <c r="P561" t="s" s="7">
-        <v>2671</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="562" ht="15.35" customHeight="1">
@@ -40213,10 +40210,10 @@
         <v>1259</v>
       </c>
       <c r="G562" t="s" s="7">
+        <v>2671</v>
+      </c>
+      <c r="H562" t="s" s="7">
         <v>2672</v>
-      </c>
-      <c r="H562" t="s" s="7">
-        <v>2673</v>
       </c>
       <c r="I562" t="s" s="7">
         <v>817</v>
@@ -40230,7 +40227,7 @@
       <c r="N562" s="9"/>
       <c r="O562" s="9"/>
       <c r="P562" t="s" s="7">
-        <v>2674</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="563" ht="15.35" customHeight="1">
@@ -40253,10 +40250,10 @@
         <v>1262</v>
       </c>
       <c r="G563" t="s" s="7">
+        <v>2674</v>
+      </c>
+      <c r="H563" t="s" s="7">
         <v>2675</v>
-      </c>
-      <c r="H563" t="s" s="7">
-        <v>2676</v>
       </c>
       <c r="I563" t="s" s="7">
         <v>817</v>
@@ -40270,7 +40267,7 @@
       <c r="N563" s="9"/>
       <c r="O563" s="9"/>
       <c r="P563" t="s" s="7">
-        <v>2677</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="564" ht="15.35" customHeight="1">
@@ -40293,7 +40290,7 @@
         <v>1266</v>
       </c>
       <c r="G564" t="s" s="7">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="H564" t="s" s="7">
         <v>879</v>
@@ -40310,7 +40307,7 @@
       <c r="N564" s="9"/>
       <c r="O564" s="9"/>
       <c r="P564" t="s" s="7">
-        <v>2679</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="565" ht="15.35" customHeight="1">
@@ -40333,10 +40330,10 @@
         <v>1617</v>
       </c>
       <c r="G565" t="s" s="7">
+        <v>2679</v>
+      </c>
+      <c r="H565" t="s" s="7">
         <v>2680</v>
-      </c>
-      <c r="H565" t="s" s="7">
-        <v>2681</v>
       </c>
       <c r="I565" t="s" s="7">
         <v>842</v>
@@ -40350,7 +40347,7 @@
       <c r="N565" s="9"/>
       <c r="O565" s="9"/>
       <c r="P565" t="s" s="7">
-        <v>2682</v>
+        <v>2681</v>
       </c>
     </row>
     <row r="566" ht="15.35" customHeight="1">
@@ -40373,10 +40370,10 @@
         <v>1621</v>
       </c>
       <c r="G566" t="s" s="7">
+        <v>2682</v>
+      </c>
+      <c r="H566" t="s" s="7">
         <v>2683</v>
-      </c>
-      <c r="H566" t="s" s="7">
-        <v>2684</v>
       </c>
       <c r="I566" t="s" s="7">
         <v>817</v>
@@ -40390,7 +40387,7 @@
       <c r="N566" s="9"/>
       <c r="O566" s="9"/>
       <c r="P566" t="s" s="7">
-        <v>2685</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="567" ht="15.35" customHeight="1">
@@ -40413,10 +40410,10 @@
         <v>1625</v>
       </c>
       <c r="G567" t="s" s="7">
+        <v>2685</v>
+      </c>
+      <c r="H567" t="s" s="7">
         <v>2686</v>
-      </c>
-      <c r="H567" t="s" s="7">
-        <v>2687</v>
       </c>
       <c r="I567" t="s" s="7">
         <v>917</v>
@@ -40430,7 +40427,7 @@
       <c r="N567" s="9"/>
       <c r="O567" s="9"/>
       <c r="P567" t="s" s="7">
-        <v>2688</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="568" ht="15.35" customHeight="1">
@@ -40453,10 +40450,10 @@
         <v>1629</v>
       </c>
       <c r="G568" t="s" s="7">
+        <v>2688</v>
+      </c>
+      <c r="H568" t="s" s="7">
         <v>2689</v>
-      </c>
-      <c r="H568" t="s" s="7">
-        <v>2690</v>
       </c>
       <c r="I568" t="s" s="7">
         <v>855</v>
@@ -40470,7 +40467,7 @@
       <c r="N568" s="9"/>
       <c r="O568" s="9"/>
       <c r="P568" t="s" s="7">
-        <v>2691</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="569" ht="15.35" customHeight="1">
@@ -40493,10 +40490,10 @@
         <v>1633</v>
       </c>
       <c r="G569" t="s" s="7">
+        <v>2691</v>
+      </c>
+      <c r="H569" t="s" s="7">
         <v>2692</v>
-      </c>
-      <c r="H569" t="s" s="7">
-        <v>2693</v>
       </c>
       <c r="I569" t="s" s="7">
         <v>817</v>
@@ -40510,7 +40507,7 @@
       <c r="N569" s="9"/>
       <c r="O569" s="9"/>
       <c r="P569" t="s" s="7">
-        <v>2694</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="570" ht="15.35" customHeight="1">
@@ -40533,10 +40530,10 @@
         <v>1637</v>
       </c>
       <c r="G570" t="s" s="7">
+        <v>2694</v>
+      </c>
+      <c r="H570" t="s" s="7">
         <v>2695</v>
-      </c>
-      <c r="H570" t="s" s="7">
-        <v>2696</v>
       </c>
       <c r="I570" t="s" s="7">
         <v>842</v>
@@ -40550,7 +40547,7 @@
       <c r="N570" s="9"/>
       <c r="O570" s="9"/>
       <c r="P570" t="s" s="7">
-        <v>2697</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="571" ht="15.35" customHeight="1">
@@ -40573,7 +40570,7 @@
         <v>1641</v>
       </c>
       <c r="G571" t="s" s="7">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="H571" t="s" s="7">
         <v>916</v>
@@ -40590,7 +40587,7 @@
       <c r="N571" s="9"/>
       <c r="O571" s="9"/>
       <c r="P571" t="s" s="7">
-        <v>2699</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="572" ht="15.35" customHeight="1">
@@ -40613,13 +40610,13 @@
         <v>1645</v>
       </c>
       <c r="G572" t="s" s="7">
+        <v>2699</v>
+      </c>
+      <c r="H572" t="s" s="7">
         <v>2700</v>
       </c>
-      <c r="H572" t="s" s="7">
-        <v>2701</v>
-      </c>
       <c r="I572" t="s" s="7">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="J572" t="s" s="7">
         <v>27</v>
@@ -40630,7 +40627,7 @@
       <c r="N572" s="9"/>
       <c r="O572" s="9"/>
       <c r="P572" t="s" s="7">
-        <v>2702</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="573" ht="15.35" customHeight="1">
@@ -40653,10 +40650,10 @@
         <v>1649</v>
       </c>
       <c r="G573" t="s" s="7">
+        <v>2702</v>
+      </c>
+      <c r="H573" t="s" s="7">
         <v>2703</v>
-      </c>
-      <c r="H573" t="s" s="7">
-        <v>2704</v>
       </c>
       <c r="I573" t="s" s="7">
         <v>842</v>
@@ -40670,7 +40667,7 @@
       <c r="N573" s="9"/>
       <c r="O573" s="9"/>
       <c r="P573" t="s" s="7">
-        <v>2705</v>
+        <v>2704</v>
       </c>
     </row>
     <row r="574" ht="15.35" customHeight="1">
@@ -40693,10 +40690,10 @@
         <v>1653</v>
       </c>
       <c r="G574" t="s" s="7">
+        <v>2705</v>
+      </c>
+      <c r="H574" t="s" s="7">
         <v>2706</v>
-      </c>
-      <c r="H574" t="s" s="7">
-        <v>2707</v>
       </c>
       <c r="I574" t="s" s="7">
         <v>817</v>
@@ -40710,7 +40707,7 @@
       <c r="N574" s="9"/>
       <c r="O574" s="9"/>
       <c r="P574" t="s" s="7">
-        <v>2708</v>
+        <v>2707</v>
       </c>
     </row>
     <row r="575" ht="15.35" customHeight="1">
@@ -40733,10 +40730,10 @@
         <v>1657</v>
       </c>
       <c r="G575" t="s" s="7">
+        <v>2708</v>
+      </c>
+      <c r="H575" t="s" s="7">
         <v>2709</v>
-      </c>
-      <c r="H575" t="s" s="7">
-        <v>2710</v>
       </c>
       <c r="I575" t="s" s="7">
         <v>817</v>
@@ -40750,7 +40747,7 @@
       <c r="N575" s="9"/>
       <c r="O575" s="9"/>
       <c r="P575" t="s" s="7">
-        <v>2711</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="576" ht="15.35" customHeight="1">
@@ -40773,10 +40770,10 @@
         <v>1661</v>
       </c>
       <c r="G576" t="s" s="7">
+        <v>2711</v>
+      </c>
+      <c r="H576" t="s" s="7">
         <v>2712</v>
-      </c>
-      <c r="H576" t="s" s="7">
-        <v>2713</v>
       </c>
       <c r="I576" t="s" s="7">
         <v>817</v>
@@ -40790,7 +40787,7 @@
       <c r="N576" s="9"/>
       <c r="O576" s="9"/>
       <c r="P576" t="s" s="7">
-        <v>2714</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="577" ht="15.35" customHeight="1">
@@ -40813,10 +40810,10 @@
         <v>1665</v>
       </c>
       <c r="G577" t="s" s="7">
+        <v>2714</v>
+      </c>
+      <c r="H577" t="s" s="7">
         <v>2715</v>
-      </c>
-      <c r="H577" t="s" s="7">
-        <v>2716</v>
       </c>
       <c r="I577" t="s" s="7">
         <v>817</v>
@@ -40830,7 +40827,7 @@
       <c r="N577" s="9"/>
       <c r="O577" s="9"/>
       <c r="P577" t="s" s="7">
-        <v>2717</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="578" ht="15.35" customHeight="1">
@@ -40853,10 +40850,10 @@
         <v>1669</v>
       </c>
       <c r="G578" t="s" s="7">
+        <v>2717</v>
+      </c>
+      <c r="H578" t="s" s="7">
         <v>2718</v>
-      </c>
-      <c r="H578" t="s" s="7">
-        <v>2719</v>
       </c>
       <c r="I578" t="s" s="7">
         <v>855</v>
@@ -40870,7 +40867,7 @@
       <c r="N578" s="9"/>
       <c r="O578" s="9"/>
       <c r="P578" t="s" s="7">
-        <v>2720</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="579" ht="15.35" customHeight="1">
@@ -40890,13 +40887,13 @@
         <v>903</v>
       </c>
       <c r="F579" t="s" s="7">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="G579" t="s" s="7">
+        <v>2720</v>
+      </c>
+      <c r="H579" t="s" s="7">
         <v>2721</v>
-      </c>
-      <c r="H579" t="s" s="7">
-        <v>2722</v>
       </c>
       <c r="I579" t="s" s="7">
         <v>855</v>
@@ -40910,7 +40907,7 @@
       <c r="N579" s="9"/>
       <c r="O579" s="9"/>
       <c r="P579" t="s" s="7">
-        <v>2723</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="580" ht="15.35" customHeight="1">
@@ -40930,13 +40927,13 @@
         <v>907</v>
       </c>
       <c r="F580" t="s" s="7">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="G580" t="s" s="7">
+        <v>2723</v>
+      </c>
+      <c r="H580" t="s" s="7">
         <v>2724</v>
-      </c>
-      <c r="H580" t="s" s="7">
-        <v>2725</v>
       </c>
       <c r="I580" t="s" s="7">
         <v>855</v>
@@ -40950,7 +40947,7 @@
       <c r="N580" s="9"/>
       <c r="O580" s="9"/>
       <c r="P580" t="s" s="7">
-        <v>2726</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="581" ht="15.35" customHeight="1">
@@ -40970,13 +40967,13 @@
         <v>907</v>
       </c>
       <c r="F581" t="s" s="7">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="G581" t="s" s="7">
+        <v>2726</v>
+      </c>
+      <c r="H581" t="s" s="7">
         <v>2727</v>
-      </c>
-      <c r="H581" t="s" s="7">
-        <v>2728</v>
       </c>
       <c r="I581" t="s" s="7">
         <v>817</v>
@@ -40990,7 +40987,7 @@
       <c r="N581" s="9"/>
       <c r="O581" s="9"/>
       <c r="P581" t="s" s="7">
-        <v>2729</v>
+        <v>2728</v>
       </c>
     </row>
     <row r="582" ht="15.35" customHeight="1">
@@ -41010,13 +41007,13 @@
         <v>907</v>
       </c>
       <c r="F582" t="s" s="7">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="G582" t="s" s="7">
+        <v>2729</v>
+      </c>
+      <c r="H582" t="s" s="7">
         <v>2730</v>
-      </c>
-      <c r="H582" t="s" s="7">
-        <v>2731</v>
       </c>
       <c r="I582" t="s" s="7">
         <v>817</v>
@@ -41030,7 +41027,7 @@
       <c r="N582" s="9"/>
       <c r="O582" s="9"/>
       <c r="P582" t="s" s="7">
-        <v>2732</v>
+        <v>2731</v>
       </c>
     </row>
     <row r="583" ht="15.35" customHeight="1">
@@ -41050,13 +41047,13 @@
         <v>911</v>
       </c>
       <c r="F583" t="s" s="7">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="G583" t="s" s="7">
+        <v>2732</v>
+      </c>
+      <c r="H583" t="s" s="7">
         <v>2733</v>
-      </c>
-      <c r="H583" t="s" s="7">
-        <v>2734</v>
       </c>
       <c r="I583" t="s" s="7">
         <v>855</v>
@@ -41070,7 +41067,7 @@
       <c r="N583" s="9"/>
       <c r="O583" s="9"/>
       <c r="P583" t="s" s="7">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="584" ht="15.35" customHeight="1">
@@ -41090,13 +41087,13 @@
         <v>911</v>
       </c>
       <c r="F584" t="s" s="7">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="G584" t="s" s="7">
+        <v>2735</v>
+      </c>
+      <c r="H584" t="s" s="7">
         <v>2736</v>
-      </c>
-      <c r="H584" t="s" s="7">
-        <v>2737</v>
       </c>
       <c r="I584" t="s" s="7">
         <v>855</v>
@@ -41110,7 +41107,7 @@
       <c r="N584" s="9"/>
       <c r="O584" s="9"/>
       <c r="P584" t="s" s="7">
-        <v>2738</v>
+        <v>2737</v>
       </c>
     </row>
     <row r="585" ht="15.35" customHeight="1">
@@ -41130,13 +41127,13 @@
         <v>911</v>
       </c>
       <c r="F585" t="s" s="7">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="G585" t="s" s="7">
+        <v>2738</v>
+      </c>
+      <c r="H585" t="s" s="7">
         <v>2739</v>
-      </c>
-      <c r="H585" t="s" s="7">
-        <v>2740</v>
       </c>
       <c r="I585" t="s" s="7">
         <v>855</v>
@@ -41150,7 +41147,7 @@
       <c r="N585" s="9"/>
       <c r="O585" s="9"/>
       <c r="P585" t="s" s="7">
-        <v>2741</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="586" ht="15.35" customHeight="1">
@@ -41170,13 +41167,13 @@
         <v>915</v>
       </c>
       <c r="F586" t="s" s="7">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="G586" t="s" s="7">
+        <v>2741</v>
+      </c>
+      <c r="H586" t="s" s="7">
         <v>2742</v>
-      </c>
-      <c r="H586" t="s" s="7">
-        <v>2743</v>
       </c>
       <c r="I586" t="s" s="7">
         <v>817</v>
@@ -41190,7 +41187,7 @@
       <c r="N586" s="9"/>
       <c r="O586" s="9"/>
       <c r="P586" t="s" s="7">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="587" ht="15.35" customHeight="1">
@@ -41210,13 +41207,13 @@
         <v>915</v>
       </c>
       <c r="F587" t="s" s="7">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="G587" t="s" s="7">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="H587" t="s" s="7">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="I587" t="s" s="7">
         <v>842</v>
@@ -41230,7 +41227,7 @@
       <c r="N587" s="9"/>
       <c r="O587" s="9"/>
       <c r="P587" t="s" s="7">
-        <v>2746</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="588" ht="15.35" customHeight="1">
@@ -41250,13 +41247,13 @@
         <v>915</v>
       </c>
       <c r="F588" t="s" s="7">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="G588" t="s" s="7">
+        <v>2746</v>
+      </c>
+      <c r="H588" t="s" s="7">
         <v>2747</v>
-      </c>
-      <c r="H588" t="s" s="7">
-        <v>2748</v>
       </c>
       <c r="I588" t="s" s="7">
         <v>817</v>
@@ -41270,7 +41267,7 @@
       <c r="N588" s="9"/>
       <c r="O588" s="9"/>
       <c r="P588" t="s" s="7">
-        <v>2749</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="589" ht="15.35" customHeight="1">
@@ -41290,13 +41287,13 @@
         <v>915</v>
       </c>
       <c r="F589" t="s" s="7">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="G589" t="s" s="7">
+        <v>2749</v>
+      </c>
+      <c r="H589" t="s" s="7">
         <v>2750</v>
-      </c>
-      <c r="H589" t="s" s="7">
-        <v>2751</v>
       </c>
       <c r="I589" t="s" s="7">
         <v>855</v>
@@ -41310,7 +41307,7 @@
       <c r="N589" s="9"/>
       <c r="O589" s="9"/>
       <c r="P589" t="s" s="7">
-        <v>2752</v>
+        <v>2751</v>
       </c>
     </row>
     <row r="590" ht="15.35" customHeight="1">
@@ -41330,13 +41327,13 @@
         <v>920</v>
       </c>
       <c r="F590" t="s" s="7">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="G590" t="s" s="7">
+        <v>2752</v>
+      </c>
+      <c r="H590" t="s" s="7">
         <v>2753</v>
-      </c>
-      <c r="H590" t="s" s="7">
-        <v>2754</v>
       </c>
       <c r="I590" t="s" s="7">
         <v>817</v>
@@ -41350,7 +41347,7 @@
       <c r="N590" s="9"/>
       <c r="O590" s="9"/>
       <c r="P590" t="s" s="7">
-        <v>2755</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="591" ht="15.35" customHeight="1">
@@ -41370,13 +41367,13 @@
         <v>920</v>
       </c>
       <c r="F591" t="s" s="7">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="G591" t="s" s="7">
+        <v>2755</v>
+      </c>
+      <c r="H591" t="s" s="7">
         <v>2756</v>
-      </c>
-      <c r="H591" t="s" s="7">
-        <v>2757</v>
       </c>
       <c r="I591" t="s" s="7">
         <v>817</v>
@@ -41390,7 +41387,7 @@
       <c r="N591" s="9"/>
       <c r="O591" s="9"/>
       <c r="P591" t="s" s="7">
-        <v>2758</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="592" ht="15.35" customHeight="1">
@@ -41410,13 +41407,13 @@
         <v>924</v>
       </c>
       <c r="F592" t="s" s="7">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="G592" t="s" s="7">
+        <v>2758</v>
+      </c>
+      <c r="H592" t="s" s="7">
         <v>2759</v>
-      </c>
-      <c r="H592" t="s" s="7">
-        <v>2760</v>
       </c>
       <c r="I592" t="s" s="7">
         <v>842</v>
@@ -41430,7 +41427,7 @@
       <c r="N592" s="9"/>
       <c r="O592" s="9"/>
       <c r="P592" t="s" s="7">
-        <v>2761</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="593" ht="15.35" customHeight="1">
@@ -41450,13 +41447,13 @@
         <v>924</v>
       </c>
       <c r="F593" t="s" s="7">
+        <v>2761</v>
+      </c>
+      <c r="G593" t="s" s="7">
         <v>2762</v>
       </c>
-      <c r="G593" t="s" s="7">
+      <c r="H593" t="s" s="7">
         <v>2763</v>
-      </c>
-      <c r="H593" t="s" s="7">
-        <v>2764</v>
       </c>
       <c r="I593" t="s" s="7">
         <v>842</v>
@@ -41470,7 +41467,7 @@
       <c r="N593" s="9"/>
       <c r="O593" s="9"/>
       <c r="P593" t="s" s="7">
-        <v>2765</v>
+        <v>2764</v>
       </c>
     </row>
     <row r="594" ht="15.35" customHeight="1">
@@ -41490,13 +41487,13 @@
         <v>924</v>
       </c>
       <c r="F594" t="s" s="7">
+        <v>2765</v>
+      </c>
+      <c r="G594" t="s" s="7">
         <v>2766</v>
       </c>
-      <c r="G594" t="s" s="7">
+      <c r="H594" t="s" s="7">
         <v>2767</v>
-      </c>
-      <c r="H594" t="s" s="7">
-        <v>2768</v>
       </c>
       <c r="I594" t="s" s="7">
         <v>842</v>
@@ -41510,7 +41507,7 @@
       <c r="N594" s="9"/>
       <c r="O594" s="9"/>
       <c r="P594" t="s" s="7">
-        <v>2769</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="595" ht="15.35" customHeight="1">
@@ -41530,13 +41527,13 @@
         <v>928</v>
       </c>
       <c r="F595" t="s" s="7">
+        <v>2769</v>
+      </c>
+      <c r="G595" t="s" s="7">
         <v>2770</v>
       </c>
-      <c r="G595" t="s" s="7">
+      <c r="H595" t="s" s="7">
         <v>2771</v>
-      </c>
-      <c r="H595" t="s" s="7">
-        <v>2772</v>
       </c>
       <c r="I595" t="s" s="7">
         <v>817</v>
@@ -41550,7 +41547,7 @@
       <c r="N595" s="9"/>
       <c r="O595" s="9"/>
       <c r="P595" t="s" s="7">
-        <v>2773</v>
+        <v>2772</v>
       </c>
     </row>
     <row r="596" ht="15.35" customHeight="1">
@@ -41570,13 +41567,13 @@
         <v>928</v>
       </c>
       <c r="F596" t="s" s="7">
+        <v>2773</v>
+      </c>
+      <c r="G596" t="s" s="7">
         <v>2774</v>
       </c>
-      <c r="G596" t="s" s="7">
+      <c r="H596" t="s" s="7">
         <v>2775</v>
-      </c>
-      <c r="H596" t="s" s="7">
-        <v>2776</v>
       </c>
       <c r="I596" t="s" s="7">
         <v>817</v>
@@ -41590,7 +41587,7 @@
       <c r="N596" s="9"/>
       <c r="O596" s="9"/>
       <c r="P596" t="s" s="7">
-        <v>2777</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="597" ht="15.35" customHeight="1">
@@ -41610,13 +41607,13 @@
         <v>928</v>
       </c>
       <c r="F597" t="s" s="7">
+        <v>2777</v>
+      </c>
+      <c r="G597" t="s" s="7">
         <v>2778</v>
       </c>
-      <c r="G597" t="s" s="7">
+      <c r="H597" t="s" s="7">
         <v>2779</v>
-      </c>
-      <c r="H597" t="s" s="7">
-        <v>2780</v>
       </c>
       <c r="I597" t="s" s="7">
         <v>817</v>
@@ -41630,7 +41627,7 @@
       <c r="N597" s="9"/>
       <c r="O597" s="9"/>
       <c r="P597" t="s" s="7">
-        <v>2781</v>
+        <v>2780</v>
       </c>
     </row>
     <row r="598" ht="15.35" customHeight="1">
@@ -41650,13 +41647,13 @@
         <v>932</v>
       </c>
       <c r="F598" t="s" s="7">
+        <v>2781</v>
+      </c>
+      <c r="G598" t="s" s="7">
         <v>2782</v>
       </c>
-      <c r="G598" t="s" s="7">
+      <c r="H598" t="s" s="7">
         <v>2783</v>
-      </c>
-      <c r="H598" t="s" s="7">
-        <v>2784</v>
       </c>
       <c r="I598" t="s" s="7">
         <v>817</v>
@@ -41670,7 +41667,7 @@
       <c r="N598" s="9"/>
       <c r="O598" s="9"/>
       <c r="P598" t="s" s="7">
-        <v>2785</v>
+        <v>2784</v>
       </c>
     </row>
     <row r="599" ht="15.35" customHeight="1">
@@ -41690,13 +41687,13 @@
         <v>932</v>
       </c>
       <c r="F599" t="s" s="7">
+        <v>2785</v>
+      </c>
+      <c r="G599" t="s" s="7">
         <v>2786</v>
       </c>
-      <c r="G599" t="s" s="7">
+      <c r="H599" t="s" s="7">
         <v>2787</v>
-      </c>
-      <c r="H599" t="s" s="7">
-        <v>2788</v>
       </c>
       <c r="I599" t="s" s="7">
         <v>817</v>
@@ -41710,7 +41707,7 @@
       <c r="N599" s="9"/>
       <c r="O599" s="9"/>
       <c r="P599" t="s" s="7">
-        <v>2789</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="600" ht="15.35" customHeight="1">
@@ -41730,16 +41727,16 @@
         <v>936</v>
       </c>
       <c r="F600" t="s" s="7">
+        <v>2789</v>
+      </c>
+      <c r="G600" t="s" s="7">
         <v>2790</v>
       </c>
-      <c r="G600" t="s" s="7">
+      <c r="H600" t="s" s="7">
         <v>2791</v>
       </c>
-      <c r="H600" t="s" s="7">
-        <v>2792</v>
-      </c>
       <c r="I600" t="s" s="7">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="J600" t="s" s="7">
         <v>27</v>
@@ -41750,7 +41747,7 @@
       <c r="N600" s="9"/>
       <c r="O600" s="9"/>
       <c r="P600" t="s" s="7">
-        <v>2793</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="601" ht="15.35" customHeight="1">
@@ -41770,13 +41767,13 @@
         <v>936</v>
       </c>
       <c r="F601" t="s" s="7">
+        <v>2793</v>
+      </c>
+      <c r="G601" t="s" s="7">
         <v>2794</v>
       </c>
-      <c r="G601" t="s" s="7">
+      <c r="H601" t="s" s="7">
         <v>2795</v>
-      </c>
-      <c r="H601" t="s" s="7">
-        <v>2796</v>
       </c>
       <c r="I601" t="s" s="7">
         <v>817</v>
@@ -41790,7 +41787,7 @@
       <c r="N601" s="9"/>
       <c r="O601" s="9"/>
       <c r="P601" t="s" s="7">
-        <v>2797</v>
+        <v>2796</v>
       </c>
     </row>
   </sheetData>
